--- a/farm_documents/Sustainable_Farm.xlsx
+++ b/farm_documents/Sustainable_Farm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29303"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ehm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5699" documentId="8_{E3A1674B-6A8A-4A99-A406-09518669CD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{733BE94E-F97D-4355-8E06-83CE2BCAD021}"/>
+  <xr:revisionPtr revIDLastSave="5700" documentId="8_{E3A1674B-6A8A-4A99-A406-09518669CD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F20B2693-28A3-4FC1-97C5-9D289973543F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="13905" firstSheet="7" activeTab="2" xr2:uid="{07024F4D-E5C7-4B8A-AB6A-143DE046C366}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="13905" firstSheet="2" activeTab="2" xr2:uid="{07024F4D-E5C7-4B8A-AB6A-143DE046C366}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall Farm" sheetId="5" r:id="rId1"/>
@@ -5972,7 +5972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="588">
+  <cellXfs count="586">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6610,177 +6610,285 @@
     <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6788,6 +6896,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6832,65 +6943,68 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6913,62 +7027,53 @@
     <xf numFmtId="0" fontId="86" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6980,12 +7085,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7000,49 +7099,31 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7052,9 +7133,6 @@
     <xf numFmtId="0" fontId="100" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7076,27 +7154,6 @@
     <xf numFmtId="0" fontId="77" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7112,6 +7169,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7130,18 +7313,6 @@
     <xf numFmtId="0" fontId="104" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -7151,188 +7322,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -12103,47 +12097,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.5" customHeight="1">
-      <c r="B1" s="398" t="s">
+      <c r="B1" s="434" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="398"/>
-      <c r="D1" s="398"/>
-      <c r="E1" s="398"/>
-      <c r="F1" s="398"/>
-      <c r="G1" s="398"/>
-      <c r="H1" s="398"/>
-      <c r="I1" s="398"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="434"/>
+      <c r="F1" s="434"/>
+      <c r="G1" s="434"/>
+      <c r="H1" s="434"/>
+      <c r="I1" s="434"/>
     </row>
     <row r="2" spans="1:9" ht="37.5" customHeight="1">
-      <c r="B2" s="398"/>
-      <c r="C2" s="398"/>
-      <c r="D2" s="398"/>
-      <c r="E2" s="398"/>
-      <c r="F2" s="398"/>
-      <c r="G2" s="398"/>
-      <c r="H2" s="398"/>
-      <c r="I2" s="398"/>
+      <c r="B2" s="434"/>
+      <c r="C2" s="434"/>
+      <c r="D2" s="434"/>
+      <c r="E2" s="434"/>
+      <c r="F2" s="434"/>
+      <c r="G2" s="434"/>
+      <c r="H2" s="434"/>
+      <c r="I2" s="434"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
-      <c r="A7" s="406" t="s">
+      <c r="A7" s="443" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="406"/>
-      <c r="C7" s="407">
+      <c r="B7" s="443"/>
+      <c r="C7" s="444">
         <v>625</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="406"/>
-      <c r="B8" s="406"/>
-      <c r="C8" s="408"/>
+      <c r="A8" s="443"/>
+      <c r="B8" s="443"/>
+      <c r="C8" s="445"/>
       <c r="D8" s="82"/>
     </row>
     <row r="9" spans="1:9" ht="27" customHeight="1">
-      <c r="A9" s="413" t="s">
+      <c r="A9" s="450" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="414"/>
+      <c r="B9" s="451"/>
       <c r="C9" s="224">
         <v>1600</v>
       </c>
@@ -12154,34 +12148,34 @@
       <c r="C10" s="221"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="H11" s="415"/>
-      <c r="I11" s="416"/>
+      <c r="H11" s="452"/>
+      <c r="I11" s="453"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="B13" s="412" t="s">
+      <c r="B13" s="449" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="412" t="s">
+      <c r="C13" s="449" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="412" t="s">
+      <c r="D13" s="449" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="412" t="s">
+      <c r="E13" s="449" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="412" t="s">
+      <c r="F13" s="449" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="412"/>
+      <c r="G13" s="449"/>
     </row>
     <row r="14" spans="1:9" ht="14.25" customHeight="1">
-      <c r="B14" s="412"/>
-      <c r="C14" s="412"/>
-      <c r="D14" s="412"/>
-      <c r="E14" s="412"/>
-      <c r="F14" s="412"/>
-      <c r="G14" s="412"/>
+      <c r="B14" s="449"/>
+      <c r="C14" s="449"/>
+      <c r="D14" s="449"/>
+      <c r="E14" s="449"/>
+      <c r="F14" s="449"/>
+      <c r="G14" s="449"/>
     </row>
     <row r="15" spans="1:9" ht="21.75" customHeight="1">
       <c r="A15" s="204" t="s">
@@ -12199,10 +12193,10 @@
       <c r="E15" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="409" t="s">
+      <c r="F15" s="446" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="409"/>
+      <c r="G15" s="446"/>
     </row>
     <row r="16" spans="1:9" ht="24.75" customHeight="1">
       <c r="A16" s="204" t="s">
@@ -12220,10 +12214,10 @@
       <c r="E16" s="62">
         <v>30</v>
       </c>
-      <c r="F16" s="410">
+      <c r="F16" s="447">
         <v>60</v>
       </c>
-      <c r="G16" s="410"/>
+      <c r="G16" s="447"/>
     </row>
     <row r="17" spans="1:23" ht="24" customHeight="1">
       <c r="A17" s="220" t="s">
@@ -12272,11 +12266,11 @@
         <f>(45000*25+2500000)/1000000</f>
         <v>3.625</v>
       </c>
-      <c r="F18" s="411">
+      <c r="F18" s="448">
         <f>(45000*50+5000000)/1000000</f>
         <v>7.25</v>
       </c>
-      <c r="G18" s="411"/>
+      <c r="G18" s="448"/>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="125"/>
@@ -12319,12 +12313,12 @@
       <c r="A22" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="371" t="s">
+      <c r="B22" s="454" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="371"/>
-      <c r="D22" s="371"/>
-      <c r="E22" s="371"/>
+      <c r="C22" s="454"/>
+      <c r="D22" s="454"/>
+      <c r="E22" s="454"/>
       <c r="F22" s="276"/>
       <c r="G22" s="276"/>
       <c r="H22" s="276"/>
@@ -12348,12 +12342,12 @@
       <c r="A23" s="226" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="372" t="s">
+      <c r="B23" s="455" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="373"/>
-      <c r="D23" s="373"/>
-      <c r="E23" s="374"/>
+      <c r="C23" s="456"/>
+      <c r="D23" s="456"/>
+      <c r="E23" s="457"/>
       <c r="F23" s="276"/>
       <c r="G23" s="276"/>
       <c r="H23" s="276"/>
@@ -12377,12 +12371,12 @@
       <c r="A24" s="226" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="371" t="s">
+      <c r="B24" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="371"/>
-      <c r="D24" s="371"/>
-      <c r="E24" s="371"/>
+      <c r="C24" s="454"/>
+      <c r="D24" s="454"/>
+      <c r="E24" s="454"/>
       <c r="F24" s="276"/>
       <c r="G24" s="276"/>
       <c r="H24" s="276"/>
@@ -12406,12 +12400,12 @@
       <c r="A25" s="226" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="372" t="s">
+      <c r="B25" s="455" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="373"/>
-      <c r="D25" s="373"/>
-      <c r="E25" s="374"/>
+      <c r="C25" s="456"/>
+      <c r="D25" s="456"/>
+      <c r="E25" s="457"/>
       <c r="F25" s="276"/>
       <c r="G25" s="276"/>
       <c r="H25" s="276"/>
@@ -12435,12 +12429,12 @@
       <c r="A26" s="226" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="372" t="s">
+      <c r="B26" s="455" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="373"/>
-      <c r="D26" s="373"/>
-      <c r="E26" s="374"/>
+      <c r="C26" s="456"/>
+      <c r="D26" s="456"/>
+      <c r="E26" s="457"/>
       <c r="F26" s="276"/>
       <c r="G26" s="276"/>
       <c r="H26" s="276"/>
@@ -12469,216 +12463,216 @@
       <c r="F27" s="62"/>
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1">
-      <c r="A29" s="399" t="s">
+      <c r="A29" s="435" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="399"/>
-      <c r="C29" s="399"/>
-      <c r="D29" s="399"/>
-      <c r="E29" s="399"/>
-      <c r="F29" s="399"/>
-      <c r="G29" s="404" t="s">
+      <c r="B29" s="435"/>
+      <c r="C29" s="435"/>
+      <c r="D29" s="435"/>
+      <c r="E29" s="435"/>
+      <c r="F29" s="435"/>
+      <c r="G29" s="441" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="404"/>
-      <c r="I29" s="404"/>
-      <c r="J29" s="404"/>
-      <c r="K29" s="404"/>
-      <c r="L29" s="404"/>
-      <c r="M29" s="404"/>
-      <c r="N29" s="404"/>
-      <c r="O29" s="404"/>
-      <c r="P29" s="404"/>
-      <c r="Q29" s="404"/>
-      <c r="R29" s="404"/>
+      <c r="H29" s="441"/>
+      <c r="I29" s="441"/>
+      <c r="J29" s="441"/>
+      <c r="K29" s="441"/>
+      <c r="L29" s="441"/>
+      <c r="M29" s="441"/>
+      <c r="N29" s="441"/>
+      <c r="O29" s="441"/>
+      <c r="P29" s="441"/>
+      <c r="Q29" s="441"/>
+      <c r="R29" s="441"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="399"/>
-      <c r="B30" s="399"/>
-      <c r="C30" s="399"/>
-      <c r="D30" s="399"/>
-      <c r="E30" s="399"/>
-      <c r="F30" s="399"/>
-      <c r="G30" s="404"/>
-      <c r="H30" s="404"/>
-      <c r="I30" s="404"/>
-      <c r="J30" s="404"/>
-      <c r="K30" s="404"/>
-      <c r="L30" s="404"/>
-      <c r="M30" s="404"/>
-      <c r="N30" s="404"/>
-      <c r="O30" s="404"/>
-      <c r="P30" s="404"/>
-      <c r="Q30" s="404"/>
-      <c r="R30" s="404"/>
+      <c r="A30" s="435"/>
+      <c r="B30" s="435"/>
+      <c r="C30" s="435"/>
+      <c r="D30" s="435"/>
+      <c r="E30" s="435"/>
+      <c r="F30" s="435"/>
+      <c r="G30" s="441"/>
+      <c r="H30" s="441"/>
+      <c r="I30" s="441"/>
+      <c r="J30" s="441"/>
+      <c r="K30" s="441"/>
+      <c r="L30" s="441"/>
+      <c r="M30" s="441"/>
+      <c r="N30" s="441"/>
+      <c r="O30" s="441"/>
+      <c r="P30" s="441"/>
+      <c r="Q30" s="441"/>
+      <c r="R30" s="441"/>
     </row>
     <row r="31" spans="1:23" ht="15">
-      <c r="A31" s="401" t="s">
+      <c r="A31" s="438" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="401"/>
-      <c r="C31" s="401"/>
-      <c r="D31" s="401"/>
-      <c r="E31" s="401"/>
-      <c r="F31" s="401"/>
-      <c r="G31" s="400" t="s">
+      <c r="B31" s="438"/>
+      <c r="C31" s="438"/>
+      <c r="D31" s="438"/>
+      <c r="E31" s="438"/>
+      <c r="F31" s="438"/>
+      <c r="G31" s="436" t="s">
         <v>30</v>
       </c>
-      <c r="H31" s="400"/>
-      <c r="I31" s="400"/>
-      <c r="J31" s="400"/>
-      <c r="K31" s="400"/>
-      <c r="L31" s="400"/>
-      <c r="M31" s="400"/>
-      <c r="N31" s="400"/>
-      <c r="O31" s="400"/>
-      <c r="P31" s="400"/>
-      <c r="Q31" s="400"/>
-      <c r="R31" s="390"/>
+      <c r="H31" s="436"/>
+      <c r="I31" s="436"/>
+      <c r="J31" s="436"/>
+      <c r="K31" s="436"/>
+      <c r="L31" s="436"/>
+      <c r="M31" s="436"/>
+      <c r="N31" s="436"/>
+      <c r="O31" s="436"/>
+      <c r="P31" s="436"/>
+      <c r="Q31" s="436"/>
+      <c r="R31" s="437"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="401"/>
-      <c r="B32" s="401"/>
-      <c r="C32" s="401"/>
-      <c r="D32" s="401"/>
-      <c r="E32" s="401"/>
-      <c r="F32" s="401"/>
-      <c r="G32" s="402" t="s">
+      <c r="A32" s="438"/>
+      <c r="B32" s="438"/>
+      <c r="C32" s="438"/>
+      <c r="D32" s="438"/>
+      <c r="E32" s="438"/>
+      <c r="F32" s="438"/>
+      <c r="G32" s="439" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="402"/>
-      <c r="I32" s="402"/>
-      <c r="J32" s="402"/>
-      <c r="K32" s="402"/>
-      <c r="L32" s="402"/>
-      <c r="M32" s="402"/>
-      <c r="N32" s="402"/>
-      <c r="O32" s="402"/>
-      <c r="P32" s="402"/>
-      <c r="Q32" s="402"/>
-      <c r="R32" s="403"/>
+      <c r="H32" s="439"/>
+      <c r="I32" s="439"/>
+      <c r="J32" s="439"/>
+      <c r="K32" s="439"/>
+      <c r="L32" s="439"/>
+      <c r="M32" s="439"/>
+      <c r="N32" s="439"/>
+      <c r="O32" s="439"/>
+      <c r="P32" s="439"/>
+      <c r="Q32" s="439"/>
+      <c r="R32" s="440"/>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1">
-      <c r="A33" s="405" t="s">
+      <c r="A33" s="442" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="405"/>
-      <c r="C33" s="405"/>
-      <c r="D33" s="405"/>
-      <c r="E33" s="405"/>
-      <c r="F33" s="405"/>
-      <c r="G33" s="400" t="s">
+      <c r="B33" s="442"/>
+      <c r="C33" s="442"/>
+      <c r="D33" s="442"/>
+      <c r="E33" s="442"/>
+      <c r="F33" s="442"/>
+      <c r="G33" s="436" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="400"/>
-      <c r="I33" s="400"/>
-      <c r="J33" s="400"/>
-      <c r="K33" s="400"/>
-      <c r="L33" s="400"/>
-      <c r="M33" s="400"/>
-      <c r="N33" s="400"/>
-      <c r="O33" s="400"/>
-      <c r="P33" s="400"/>
-      <c r="Q33" s="400"/>
-      <c r="R33" s="390"/>
+      <c r="H33" s="436"/>
+      <c r="I33" s="436"/>
+      <c r="J33" s="436"/>
+      <c r="K33" s="436"/>
+      <c r="L33" s="436"/>
+      <c r="M33" s="436"/>
+      <c r="N33" s="436"/>
+      <c r="O33" s="436"/>
+      <c r="P33" s="436"/>
+      <c r="Q33" s="436"/>
+      <c r="R33" s="437"/>
     </row>
     <row r="34" spans="1:20" ht="15" customHeight="1">
-      <c r="A34" s="389" t="s">
+      <c r="A34" s="469" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="389"/>
-      <c r="C34" s="389"/>
-      <c r="D34" s="389"/>
-      <c r="E34" s="389"/>
-      <c r="F34" s="389"/>
-      <c r="G34" s="385" t="s">
+      <c r="B34" s="469"/>
+      <c r="C34" s="469"/>
+      <c r="D34" s="469"/>
+      <c r="E34" s="469"/>
+      <c r="F34" s="469"/>
+      <c r="G34" s="465" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="385"/>
-      <c r="I34" s="385"/>
-      <c r="J34" s="385"/>
-      <c r="K34" s="385"/>
-      <c r="L34" s="385"/>
-      <c r="M34" s="385"/>
-      <c r="N34" s="385"/>
-      <c r="O34" s="385"/>
-      <c r="P34" s="385"/>
-      <c r="Q34" s="385"/>
-      <c r="R34" s="386"/>
+      <c r="H34" s="465"/>
+      <c r="I34" s="465"/>
+      <c r="J34" s="465"/>
+      <c r="K34" s="465"/>
+      <c r="L34" s="465"/>
+      <c r="M34" s="465"/>
+      <c r="N34" s="465"/>
+      <c r="O34" s="465"/>
+      <c r="P34" s="465"/>
+      <c r="Q34" s="465"/>
+      <c r="R34" s="466"/>
     </row>
     <row r="35" spans="1:20" ht="15" customHeight="1">
-      <c r="A35" s="389" t="s">
+      <c r="A35" s="469" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="389"/>
-      <c r="C35" s="389"/>
-      <c r="D35" s="389"/>
-      <c r="E35" s="389"/>
-      <c r="F35" s="389"/>
-      <c r="G35" s="387" t="s">
+      <c r="B35" s="469"/>
+      <c r="C35" s="469"/>
+      <c r="D35" s="469"/>
+      <c r="E35" s="469"/>
+      <c r="F35" s="469"/>
+      <c r="G35" s="467" t="s">
         <v>37</v>
       </c>
-      <c r="H35" s="387"/>
-      <c r="I35" s="387"/>
-      <c r="J35" s="387"/>
-      <c r="K35" s="387"/>
-      <c r="L35" s="387"/>
-      <c r="M35" s="387"/>
-      <c r="N35" s="387"/>
-      <c r="O35" s="387"/>
-      <c r="P35" s="387"/>
-      <c r="Q35" s="387"/>
-      <c r="R35" s="388"/>
+      <c r="H35" s="467"/>
+      <c r="I35" s="467"/>
+      <c r="J35" s="467"/>
+      <c r="K35" s="467"/>
+      <c r="L35" s="467"/>
+      <c r="M35" s="467"/>
+      <c r="N35" s="467"/>
+      <c r="O35" s="467"/>
+      <c r="P35" s="467"/>
+      <c r="Q35" s="467"/>
+      <c r="R35" s="468"/>
       <c r="S35" s="29"/>
       <c r="T35" s="29"/>
     </row>
     <row r="36" spans="1:20" ht="15" customHeight="1">
-      <c r="A36" s="389" t="s">
+      <c r="A36" s="469" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="389"/>
-      <c r="C36" s="389"/>
-      <c r="D36" s="389"/>
-      <c r="E36" s="389"/>
-      <c r="F36" s="389"/>
-      <c r="G36" s="390" t="s">
+      <c r="B36" s="469"/>
+      <c r="C36" s="469"/>
+      <c r="D36" s="469"/>
+      <c r="E36" s="469"/>
+      <c r="F36" s="469"/>
+      <c r="G36" s="437" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="390"/>
-      <c r="I36" s="390"/>
-      <c r="J36" s="390"/>
-      <c r="K36" s="390"/>
-      <c r="L36" s="390"/>
-      <c r="M36" s="390"/>
-      <c r="N36" s="390"/>
-      <c r="O36" s="390"/>
-      <c r="P36" s="390"/>
-      <c r="Q36" s="390"/>
-      <c r="R36" s="390"/>
+      <c r="H36" s="437"/>
+      <c r="I36" s="437"/>
+      <c r="J36" s="437"/>
+      <c r="K36" s="437"/>
+      <c r="L36" s="437"/>
+      <c r="M36" s="437"/>
+      <c r="N36" s="437"/>
+      <c r="O36" s="437"/>
+      <c r="P36" s="437"/>
+      <c r="Q36" s="437"/>
+      <c r="R36" s="437"/>
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1">
-      <c r="A37" s="389" t="s">
+      <c r="A37" s="469" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="389"/>
-      <c r="C37" s="389"/>
-      <c r="D37" s="389"/>
-      <c r="E37" s="389"/>
-      <c r="F37" s="389"/>
-      <c r="G37" s="390" t="s">
+      <c r="B37" s="469"/>
+      <c r="C37" s="469"/>
+      <c r="D37" s="469"/>
+      <c r="E37" s="469"/>
+      <c r="F37" s="469"/>
+      <c r="G37" s="437" t="s">
         <v>41</v>
       </c>
-      <c r="H37" s="390"/>
-      <c r="I37" s="390"/>
-      <c r="J37" s="390"/>
-      <c r="K37" s="390"/>
-      <c r="L37" s="390"/>
-      <c r="M37" s="390"/>
-      <c r="N37" s="390"/>
-      <c r="O37" s="390"/>
-      <c r="P37" s="390"/>
-      <c r="Q37" s="390"/>
-      <c r="R37" s="390"/>
+      <c r="H37" s="437"/>
+      <c r="I37" s="437"/>
+      <c r="J37" s="437"/>
+      <c r="K37" s="437"/>
+      <c r="L37" s="437"/>
+      <c r="M37" s="437"/>
+      <c r="N37" s="437"/>
+      <c r="O37" s="437"/>
+      <c r="P37" s="437"/>
+      <c r="Q37" s="437"/>
+      <c r="R37" s="437"/>
     </row>
     <row r="38" spans="1:20">
       <c r="F38" s="30"/>
@@ -12686,11 +12680,11 @@
     <row r="39" spans="1:20" ht="15" customHeight="1">
       <c r="A39" s="41"/>
       <c r="B39" s="41"/>
-      <c r="C39" s="376"/>
-      <c r="D39" s="376"/>
-      <c r="E39" s="376"/>
-      <c r="F39" s="375"/>
-      <c r="G39" s="375"/>
+      <c r="C39" s="459"/>
+      <c r="D39" s="459"/>
+      <c r="E39" s="459"/>
+      <c r="F39" s="458"/>
+      <c r="G39" s="458"/>
     </row>
     <row r="40" spans="1:20" ht="14.25" customHeight="1">
       <c r="C40" s="82"/>
@@ -12698,51 +12692,51 @@
       <c r="E40" s="86"/>
       <c r="F40" s="86"/>
       <c r="G40" s="82"/>
-      <c r="L40" s="350"/>
-      <c r="M40" s="350"/>
-      <c r="N40" s="350"/>
+      <c r="L40" s="474"/>
+      <c r="M40" s="474"/>
+      <c r="N40" s="474"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1">
-      <c r="A41" s="391" t="s">
+      <c r="A41" s="470" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="391" t="str">
+      <c r="B41" s="470" t="str">
         <f>A29</f>
         <v>Part of the Farm</v>
       </c>
-      <c r="C41" s="392" t="s">
+      <c r="C41" s="471" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="392"/>
-      <c r="E41" s="392" t="str">
+      <c r="D41" s="471"/>
+      <c r="E41" s="471" t="str">
         <f>A15</f>
         <v>Location</v>
       </c>
-      <c r="F41" s="384" t="s">
+      <c r="F41" s="464" t="s">
         <v>44</v>
       </c>
       <c r="G41" s="127"/>
-      <c r="L41" s="350"/>
-      <c r="M41" s="350"/>
-      <c r="N41" s="350"/>
+      <c r="L41" s="474"/>
+      <c r="M41" s="474"/>
+      <c r="N41" s="474"/>
     </row>
     <row r="42" spans="1:20" ht="14.25" customHeight="1">
-      <c r="A42" s="391"/>
-      <c r="B42" s="391"/>
-      <c r="C42" s="392"/>
-      <c r="D42" s="392"/>
-      <c r="E42" s="392"/>
-      <c r="F42" s="384"/>
+      <c r="A42" s="470"/>
+      <c r="B42" s="470"/>
+      <c r="C42" s="471"/>
+      <c r="D42" s="471"/>
+      <c r="E42" s="471"/>
+      <c r="F42" s="464"/>
       <c r="G42" s="127"/>
-      <c r="L42" s="349"/>
-      <c r="M42" s="349"/>
-      <c r="N42" s="349"/>
+      <c r="L42" s="473"/>
+      <c r="M42" s="473"/>
+      <c r="N42" s="473"/>
     </row>
     <row r="43" spans="1:20" ht="30" customHeight="1">
-      <c r="A43" s="345" t="s">
+      <c r="A43" s="472" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="393" t="str">
+      <c r="B43" s="384" t="str">
         <f>A31</f>
         <v>Energy Supply system (Solar PV power plant,Solar Tracking)</v>
       </c>
@@ -12752,131 +12746,131 @@
       <c r="D43" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="380" t="s">
+      <c r="E43" s="460" t="s">
         <v>9</v>
       </c>
-      <c r="F43" s="360" t="s">
+      <c r="F43" s="391" t="s">
         <v>13</v>
       </c>
-      <c r="L43" s="349"/>
-      <c r="M43" s="349"/>
-      <c r="N43" s="349"/>
+      <c r="L43" s="473"/>
+      <c r="M43" s="473"/>
+      <c r="N43" s="473"/>
     </row>
     <row r="44" spans="1:20" ht="15">
-      <c r="A44" s="346"/>
-      <c r="B44" s="394"/>
+      <c r="A44" s="383"/>
+      <c r="B44" s="385"/>
       <c r="C44" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D44" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E44" s="381"/>
-      <c r="F44" s="360"/>
-      <c r="L44" s="349"/>
-      <c r="M44" s="349"/>
-      <c r="N44" s="349"/>
+      <c r="E44" s="461"/>
+      <c r="F44" s="391"/>
+      <c r="L44" s="473"/>
+      <c r="M44" s="473"/>
+      <c r="N44" s="473"/>
     </row>
     <row r="45" spans="1:20" ht="15">
-      <c r="A45" s="346"/>
-      <c r="B45" s="394"/>
+      <c r="A45" s="383"/>
+      <c r="B45" s="385"/>
       <c r="C45" s="63" t="s">
         <v>49</v>
       </c>
       <c r="D45" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E45" s="381"/>
-      <c r="F45" s="360"/>
-      <c r="L45" s="349"/>
-      <c r="M45" s="349"/>
-      <c r="N45" s="349"/>
+      <c r="E45" s="461"/>
+      <c r="F45" s="391"/>
+      <c r="L45" s="473"/>
+      <c r="M45" s="473"/>
+      <c r="N45" s="473"/>
     </row>
     <row r="46" spans="1:20" ht="15">
-      <c r="A46" s="346"/>
-      <c r="B46" s="394"/>
-      <c r="C46" s="369" t="s">
+      <c r="A46" s="383"/>
+      <c r="B46" s="385"/>
+      <c r="C46" s="432" t="s">
         <v>51</v>
       </c>
       <c r="D46" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="381"/>
-      <c r="F46" s="360"/>
-      <c r="L46" s="349"/>
-      <c r="M46" s="349"/>
-      <c r="N46" s="349"/>
+      <c r="E46" s="461"/>
+      <c r="F46" s="391"/>
+      <c r="L46" s="473"/>
+      <c r="M46" s="473"/>
+      <c r="N46" s="473"/>
     </row>
     <row r="47" spans="1:20" ht="15">
-      <c r="A47" s="346"/>
-      <c r="B47" s="394"/>
-      <c r="C47" s="370"/>
+      <c r="A47" s="383"/>
+      <c r="B47" s="385"/>
+      <c r="C47" s="433"/>
       <c r="D47" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="382"/>
-      <c r="F47" s="360"/>
-      <c r="L47" s="349"/>
-      <c r="M47" s="349"/>
-      <c r="N47" s="349"/>
+      <c r="E47" s="462"/>
+      <c r="F47" s="391"/>
+      <c r="L47" s="473"/>
+      <c r="M47" s="473"/>
+      <c r="N47" s="473"/>
     </row>
     <row r="48" spans="1:20" ht="15">
-      <c r="A48" s="346"/>
-      <c r="B48" s="394"/>
-      <c r="C48" s="370"/>
+      <c r="A48" s="383"/>
+      <c r="B48" s="385"/>
+      <c r="C48" s="433"/>
       <c r="D48" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="E48" s="382"/>
-      <c r="F48" s="360"/>
-      <c r="L48" s="349"/>
-      <c r="M48" s="349"/>
-      <c r="N48" s="349"/>
+      <c r="E48" s="462"/>
+      <c r="F48" s="391"/>
+      <c r="L48" s="473"/>
+      <c r="M48" s="473"/>
+      <c r="N48" s="473"/>
     </row>
     <row r="49" spans="1:14" ht="15">
-      <c r="A49" s="346"/>
-      <c r="B49" s="394"/>
-      <c r="C49" s="370"/>
+      <c r="A49" s="383"/>
+      <c r="B49" s="385"/>
+      <c r="C49" s="433"/>
       <c r="D49" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="382"/>
-      <c r="F49" s="360"/>
-      <c r="L49" s="349"/>
-      <c r="M49" s="349"/>
-      <c r="N49" s="349"/>
+      <c r="E49" s="462"/>
+      <c r="F49" s="391"/>
+      <c r="L49" s="473"/>
+      <c r="M49" s="473"/>
+      <c r="N49" s="473"/>
     </row>
     <row r="50" spans="1:14" ht="15">
-      <c r="A50" s="346"/>
-      <c r="B50" s="394"/>
-      <c r="C50" s="370"/>
+      <c r="A50" s="383"/>
+      <c r="B50" s="385"/>
+      <c r="C50" s="433"/>
       <c r="D50" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="382"/>
-      <c r="F50" s="360"/>
-      <c r="L50" s="349"/>
-      <c r="M50" s="349"/>
-      <c r="N50" s="349"/>
+      <c r="E50" s="462"/>
+      <c r="F50" s="391"/>
+      <c r="L50" s="473"/>
+      <c r="M50" s="473"/>
+      <c r="N50" s="473"/>
     </row>
     <row r="51" spans="1:14" ht="15">
-      <c r="A51" s="346"/>
-      <c r="B51" s="394"/>
+      <c r="A51" s="383"/>
+      <c r="B51" s="385"/>
       <c r="C51" s="71" t="s">
         <v>57</v>
       </c>
       <c r="D51" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="381"/>
-      <c r="F51" s="361"/>
-      <c r="L51" s="349"/>
-      <c r="M51" s="349"/>
-      <c r="N51" s="349"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="392"/>
+      <c r="L51" s="473"/>
+      <c r="M51" s="473"/>
+      <c r="N51" s="473"/>
     </row>
     <row r="52" spans="1:14" ht="15">
-      <c r="A52" s="346"/>
-      <c r="B52" s="351" t="str">
+      <c r="A52" s="383"/>
+      <c r="B52" s="396" t="str">
         <f>A33</f>
         <v>Irrigation system</v>
       </c>
@@ -12886,83 +12880,83 @@
       <c r="D52" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="E52" s="381"/>
-      <c r="F52" s="362"/>
-      <c r="L52" s="349"/>
-      <c r="M52" s="349"/>
-      <c r="N52" s="349"/>
+      <c r="E52" s="461"/>
+      <c r="F52" s="397"/>
+      <c r="L52" s="473"/>
+      <c r="M52" s="473"/>
+      <c r="N52" s="473"/>
     </row>
     <row r="53" spans="1:14" ht="15" customHeight="1">
-      <c r="A53" s="346"/>
-      <c r="B53" s="351"/>
+      <c r="A53" s="383"/>
+      <c r="B53" s="396"/>
       <c r="C53" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D53" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="381"/>
-      <c r="F53" s="363"/>
+      <c r="E53" s="461"/>
+      <c r="F53" s="398"/>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
-      <c r="A54" s="346"/>
-      <c r="B54" s="351"/>
+      <c r="A54" s="383"/>
+      <c r="B54" s="396"/>
       <c r="C54" s="71" t="s">
         <v>49</v>
       </c>
       <c r="D54" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="E54" s="381"/>
-      <c r="F54" s="363"/>
+      <c r="E54" s="461"/>
+      <c r="F54" s="398"/>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
-      <c r="A55" s="346"/>
-      <c r="B55" s="351"/>
-      <c r="C55" s="352" t="s">
+      <c r="A55" s="383"/>
+      <c r="B55" s="396"/>
+      <c r="C55" s="400" t="s">
         <v>51</v>
       </c>
       <c r="D55" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="E55" s="381"/>
-      <c r="F55" s="363"/>
+      <c r="E55" s="461"/>
+      <c r="F55" s="398"/>
     </row>
     <row r="56" spans="1:14" ht="15" customHeight="1">
-      <c r="A56" s="346"/>
-      <c r="B56" s="351"/>
-      <c r="C56" s="353"/>
+      <c r="A56" s="383"/>
+      <c r="B56" s="396"/>
+      <c r="C56" s="401"/>
       <c r="D56" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="E56" s="381"/>
-      <c r="F56" s="363"/>
+      <c r="E56" s="461"/>
+      <c r="F56" s="398"/>
     </row>
     <row r="57" spans="1:14" ht="15" customHeight="1">
-      <c r="A57" s="346"/>
-      <c r="B57" s="351"/>
-      <c r="C57" s="354"/>
+      <c r="A57" s="383"/>
+      <c r="B57" s="396"/>
+      <c r="C57" s="402"/>
       <c r="D57" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E57" s="381"/>
-      <c r="F57" s="363"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="398"/>
     </row>
     <row r="58" spans="1:14" ht="15" customHeight="1">
-      <c r="A58" s="346"/>
-      <c r="B58" s="351"/>
+      <c r="A58" s="383"/>
+      <c r="B58" s="396"/>
       <c r="C58" s="72" t="s">
         <v>57</v>
       </c>
       <c r="D58" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="381"/>
-      <c r="F58" s="364"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="399"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="346"/>
-      <c r="B59" s="355" t="str">
+      <c r="A59" s="383"/>
+      <c r="B59" s="403" t="str">
         <f t="shared" ref="B59" si="0">A34</f>
         <v>Crop Storage (Smart Dryer)</v>
       </c>
@@ -12972,62 +12966,62 @@
       <c r="D59" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="E59" s="381"/>
-      <c r="F59" s="357" t="s">
+      <c r="E59" s="461"/>
+      <c r="F59" s="425" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="346"/>
-      <c r="B60" s="367"/>
+      <c r="A60" s="383"/>
+      <c r="B60" s="404"/>
       <c r="C60" s="89" t="s">
         <v>47</v>
       </c>
       <c r="D60" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="E60" s="381"/>
-      <c r="F60" s="358"/>
+      <c r="E60" s="461"/>
+      <c r="F60" s="426"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="346"/>
-      <c r="B61" s="367"/>
+      <c r="A61" s="383"/>
+      <c r="B61" s="404"/>
       <c r="C61" s="89" t="s">
         <v>49</v>
       </c>
       <c r="D61" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="E61" s="381"/>
-      <c r="F61" s="358"/>
+      <c r="E61" s="461"/>
+      <c r="F61" s="426"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="346"/>
-      <c r="B62" s="367"/>
+      <c r="A62" s="383"/>
+      <c r="B62" s="404"/>
       <c r="C62" s="89" t="s">
         <v>51</v>
       </c>
       <c r="D62" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="381"/>
-      <c r="F62" s="358"/>
+      <c r="E62" s="461"/>
+      <c r="F62" s="426"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="346"/>
-      <c r="B63" s="368"/>
+      <c r="A63" s="383"/>
+      <c r="B63" s="405"/>
       <c r="C63" s="90" t="s">
         <v>57</v>
       </c>
       <c r="D63" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="381"/>
-      <c r="F63" s="359"/>
+      <c r="E63" s="461"/>
+      <c r="F63" s="427"/>
     </row>
     <row r="64" spans="1:14" ht="28.5" customHeight="1">
-      <c r="A64" s="346"/>
-      <c r="B64" s="393" t="str">
+      <c r="A64" s="383"/>
+      <c r="B64" s="384" t="str">
         <f>A35</f>
         <v>Fencing and Security (Face Recognition)</v>
       </c>
@@ -13037,62 +13031,62 @@
       <c r="D64" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="381"/>
-      <c r="F64" s="365" t="s">
+      <c r="E64" s="461"/>
+      <c r="F64" s="390" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1">
-      <c r="A65" s="346"/>
-      <c r="B65" s="394"/>
+      <c r="A65" s="383"/>
+      <c r="B65" s="385"/>
       <c r="C65" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D65" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="E65" s="381"/>
-      <c r="F65" s="360"/>
+      <c r="E65" s="461"/>
+      <c r="F65" s="391"/>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1">
-      <c r="A66" s="346"/>
-      <c r="B66" s="394"/>
+      <c r="A66" s="383"/>
+      <c r="B66" s="385"/>
       <c r="C66" s="63" t="s">
         <v>49</v>
       </c>
       <c r="D66" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E66" s="381"/>
-      <c r="F66" s="360"/>
+      <c r="E66" s="461"/>
+      <c r="F66" s="391"/>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1">
-      <c r="A67" s="346"/>
-      <c r="B67" s="394"/>
+      <c r="A67" s="383"/>
+      <c r="B67" s="385"/>
       <c r="C67" s="63" t="s">
         <v>51</v>
       </c>
       <c r="D67" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="E67" s="381"/>
-      <c r="F67" s="360"/>
+      <c r="E67" s="461"/>
+      <c r="F67" s="391"/>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1">
-      <c r="A68" s="346"/>
-      <c r="B68" s="394"/>
+      <c r="A68" s="383"/>
+      <c r="B68" s="385"/>
       <c r="C68" s="71" t="s">
         <v>57</v>
       </c>
       <c r="D68" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E68" s="381"/>
-      <c r="F68" s="361"/>
+      <c r="E68" s="461"/>
+      <c r="F68" s="392"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="346"/>
-      <c r="B69" s="355" t="str">
+      <c r="A69" s="383"/>
+      <c r="B69" s="403" t="str">
         <f>A36</f>
         <v>Visitors Management (No Reesa)</v>
       </c>
@@ -13102,62 +13096,62 @@
       <c r="D69" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="E69" s="381"/>
-      <c r="F69" s="366" t="s">
+      <c r="E69" s="461"/>
+      <c r="F69" s="411" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="346"/>
-      <c r="B70" s="355"/>
+      <c r="A70" s="383"/>
+      <c r="B70" s="403"/>
       <c r="C70" s="130" t="s">
         <v>47</v>
       </c>
       <c r="D70" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="E70" s="381"/>
-      <c r="F70" s="360"/>
+      <c r="E70" s="461"/>
+      <c r="F70" s="391"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="346"/>
-      <c r="B71" s="355"/>
+      <c r="A71" s="383"/>
+      <c r="B71" s="403"/>
       <c r="C71" s="130" t="s">
         <v>49</v>
       </c>
       <c r="D71" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="E71" s="381"/>
-      <c r="F71" s="360"/>
+      <c r="E71" s="461"/>
+      <c r="F71" s="391"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="346"/>
-      <c r="B72" s="355"/>
+      <c r="A72" s="383"/>
+      <c r="B72" s="403"/>
       <c r="C72" s="130" t="s">
         <v>51</v>
       </c>
       <c r="D72" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="381"/>
-      <c r="F72" s="360"/>
+      <c r="E72" s="461"/>
+      <c r="F72" s="391"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="346"/>
-      <c r="B73" s="356"/>
+      <c r="A73" s="383"/>
+      <c r="B73" s="421"/>
       <c r="C73" s="131" t="s">
         <v>57</v>
       </c>
       <c r="D73" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="E73" s="381"/>
-      <c r="F73" s="361"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="392"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="346"/>
-      <c r="B74" s="347" t="str">
+      <c r="A74" s="383"/>
+      <c r="B74" s="431" t="str">
         <f>A37</f>
         <v>Product Transformation System (Ball mill grinder)</v>
       </c>
@@ -13167,94 +13161,94 @@
       <c r="D74" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="E74" s="381"/>
-      <c r="F74" s="366" t="s">
+      <c r="E74" s="461"/>
+      <c r="F74" s="411" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="346"/>
-      <c r="B75" s="348"/>
+      <c r="A75" s="383"/>
+      <c r="B75" s="409"/>
       <c r="C75" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D75" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E75" s="381"/>
-      <c r="F75" s="360"/>
+      <c r="E75" s="461"/>
+      <c r="F75" s="391"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="346"/>
-      <c r="B76" s="348"/>
+      <c r="A76" s="383"/>
+      <c r="B76" s="409"/>
       <c r="C76" s="75" t="s">
         <v>49</v>
       </c>
       <c r="D76" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E76" s="381"/>
-      <c r="F76" s="360"/>
+      <c r="E76" s="461"/>
+      <c r="F76" s="391"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="346"/>
-      <c r="B77" s="348"/>
-      <c r="C77" s="377" t="s">
+      <c r="A77" s="383"/>
+      <c r="B77" s="409"/>
+      <c r="C77" s="412" t="s">
         <v>51</v>
       </c>
       <c r="D77" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E77" s="381"/>
-      <c r="F77" s="360"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="391"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="346"/>
-      <c r="B78" s="348"/>
-      <c r="C78" s="378"/>
+      <c r="A78" s="383"/>
+      <c r="B78" s="409"/>
+      <c r="C78" s="413"/>
       <c r="D78" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="E78" s="381"/>
-      <c r="F78" s="360"/>
+      <c r="E78" s="461"/>
+      <c r="F78" s="391"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="346"/>
-      <c r="B79" s="348"/>
-      <c r="C79" s="378"/>
+      <c r="A79" s="383"/>
+      <c r="B79" s="409"/>
+      <c r="C79" s="413"/>
       <c r="D79" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="E79" s="381"/>
-      <c r="F79" s="360"/>
+      <c r="E79" s="461"/>
+      <c r="F79" s="391"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="346"/>
-      <c r="B80" s="348"/>
-      <c r="C80" s="379"/>
+      <c r="A80" s="383"/>
+      <c r="B80" s="409"/>
+      <c r="C80" s="414"/>
       <c r="D80" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="E80" s="381"/>
-      <c r="F80" s="360"/>
+      <c r="E80" s="461"/>
+      <c r="F80" s="391"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="346"/>
-      <c r="B81" s="348"/>
+      <c r="A81" s="383"/>
+      <c r="B81" s="409"/>
       <c r="C81" s="80" t="s">
         <v>57</v>
       </c>
       <c r="D81" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E81" s="383"/>
-      <c r="F81" s="361"/>
+      <c r="E81" s="463"/>
+      <c r="F81" s="392"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="346" t="s">
+      <c r="A82" s="383" t="s">
         <v>76</v>
       </c>
-      <c r="B82" s="348" t="s">
+      <c r="B82" s="409" t="s">
         <v>29</v>
       </c>
       <c r="C82" s="73" t="s">
@@ -13264,104 +13258,104 @@
         <f>(9450000+72000000)/1000000</f>
         <v>81.45</v>
       </c>
-      <c r="E82" s="425" t="s">
+      <c r="E82" s="415" t="s">
         <v>10</v>
       </c>
-      <c r="F82" s="365">
+      <c r="F82" s="390">
         <v>2500</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="346"/>
-      <c r="B83" s="348"/>
+      <c r="A83" s="383"/>
+      <c r="B83" s="409"/>
       <c r="C83" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D83" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E83" s="426"/>
-      <c r="F83" s="360"/>
+      <c r="E83" s="416"/>
+      <c r="F83" s="391"/>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="346"/>
-      <c r="B84" s="348"/>
+      <c r="A84" s="383"/>
+      <c r="B84" s="409"/>
       <c r="C84" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D84" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E84" s="426"/>
-      <c r="F84" s="360"/>
+      <c r="E84" s="416"/>
+      <c r="F84" s="391"/>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="346"/>
-      <c r="B85" s="348"/>
-      <c r="C85" s="429" t="s">
+      <c r="A85" s="383"/>
+      <c r="B85" s="409"/>
+      <c r="C85" s="419" t="s">
         <v>51</v>
       </c>
       <c r="D85" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="E85" s="426"/>
-      <c r="F85" s="360"/>
+      <c r="E85" s="416"/>
+      <c r="F85" s="391"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="346"/>
-      <c r="B86" s="348"/>
-      <c r="C86" s="430"/>
+      <c r="A86" s="383"/>
+      <c r="B86" s="409"/>
+      <c r="C86" s="420"/>
       <c r="D86" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="E86" s="427"/>
-      <c r="F86" s="360"/>
+      <c r="E86" s="417"/>
+      <c r="F86" s="391"/>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="346"/>
-      <c r="B87" s="348"/>
-      <c r="C87" s="430"/>
+      <c r="A87" s="383"/>
+      <c r="B87" s="409"/>
+      <c r="C87" s="420"/>
       <c r="D87" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="E87" s="427"/>
-      <c r="F87" s="360"/>
+      <c r="E87" s="417"/>
+      <c r="F87" s="391"/>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="346"/>
-      <c r="B88" s="348"/>
-      <c r="C88" s="430"/>
+      <c r="A88" s="383"/>
+      <c r="B88" s="409"/>
+      <c r="C88" s="420"/>
       <c r="D88" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="427"/>
-      <c r="F88" s="360"/>
+      <c r="E88" s="417"/>
+      <c r="F88" s="391"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="346"/>
-      <c r="B89" s="348"/>
-      <c r="C89" s="430"/>
+      <c r="A89" s="383"/>
+      <c r="B89" s="409"/>
+      <c r="C89" s="420"/>
       <c r="D89" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="E89" s="427"/>
-      <c r="F89" s="360"/>
+      <c r="E89" s="417"/>
+      <c r="F89" s="391"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="346"/>
-      <c r="B90" s="417"/>
+      <c r="A90" s="383"/>
+      <c r="B90" s="410"/>
       <c r="C90" s="75" t="s">
         <v>57</v>
       </c>
       <c r="D90" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="E90" s="426"/>
-      <c r="F90" s="361"/>
+      <c r="E90" s="416"/>
+      <c r="F90" s="392"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="346"/>
-      <c r="B91" s="367" t="s">
+      <c r="A91" s="383"/>
+      <c r="B91" s="404" t="s">
         <v>32</v>
       </c>
       <c r="C91" s="73" t="s">
@@ -13371,80 +13365,80 @@
         <f>1035827/1000000</f>
         <v>1.0358270000000001</v>
       </c>
-      <c r="E91" s="426"/>
-      <c r="F91" s="362"/>
+      <c r="E91" s="416"/>
+      <c r="F91" s="397"/>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="346"/>
-      <c r="B92" s="355"/>
+      <c r="A92" s="383"/>
+      <c r="B92" s="403"/>
       <c r="C92" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D92" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="E92" s="426"/>
-      <c r="F92" s="363"/>
+      <c r="E92" s="416"/>
+      <c r="F92" s="398"/>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="346"/>
-      <c r="B93" s="355"/>
+      <c r="A93" s="383"/>
+      <c r="B93" s="403"/>
       <c r="C93" s="75" t="s">
         <v>49</v>
       </c>
       <c r="D93" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="E93" s="426"/>
-      <c r="F93" s="363"/>
+      <c r="E93" s="416"/>
+      <c r="F93" s="398"/>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="346"/>
-      <c r="B94" s="355"/>
-      <c r="C94" s="431" t="s">
+      <c r="A94" s="383"/>
+      <c r="B94" s="403"/>
+      <c r="C94" s="422" t="s">
         <v>51</v>
       </c>
       <c r="D94" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="426"/>
-      <c r="F94" s="363"/>
+      <c r="E94" s="416"/>
+      <c r="F94" s="398"/>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="346"/>
-      <c r="B95" s="355"/>
-      <c r="C95" s="432"/>
+      <c r="A95" s="383"/>
+      <c r="B95" s="403"/>
+      <c r="C95" s="423"/>
       <c r="D95" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="E95" s="426"/>
-      <c r="F95" s="363"/>
+      <c r="E95" s="416"/>
+      <c r="F95" s="398"/>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="346"/>
-      <c r="B96" s="355"/>
-      <c r="C96" s="433"/>
+      <c r="A96" s="383"/>
+      <c r="B96" s="403"/>
+      <c r="C96" s="424"/>
       <c r="D96" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E96" s="426"/>
-      <c r="F96" s="363"/>
+      <c r="E96" s="416"/>
+      <c r="F96" s="398"/>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="346"/>
-      <c r="B97" s="356"/>
+      <c r="A97" s="383"/>
+      <c r="B97" s="421"/>
       <c r="C97" s="80" t="s">
         <v>57</v>
       </c>
       <c r="D97" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E97" s="426"/>
-      <c r="F97" s="364"/>
+      <c r="E97" s="416"/>
+      <c r="F97" s="399"/>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="346"/>
-      <c r="B98" s="367" t="s">
+      <c r="A98" s="383"/>
+      <c r="B98" s="404" t="s">
         <v>34</v>
       </c>
       <c r="C98" s="88" t="s">
@@ -13454,62 +13448,62 @@
         <f>5000000/1000000</f>
         <v>5</v>
       </c>
-      <c r="E98" s="426"/>
-      <c r="F98" s="357" t="s">
+      <c r="E98" s="416"/>
+      <c r="F98" s="425" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="346"/>
-      <c r="B99" s="367"/>
+      <c r="A99" s="383"/>
+      <c r="B99" s="404"/>
       <c r="C99" s="89" t="s">
         <v>47</v>
       </c>
       <c r="D99" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="E99" s="426"/>
-      <c r="F99" s="358"/>
+      <c r="E99" s="416"/>
+      <c r="F99" s="426"/>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="346"/>
-      <c r="B100" s="367"/>
+      <c r="A100" s="383"/>
+      <c r="B100" s="404"/>
       <c r="C100" s="89" t="s">
         <v>49</v>
       </c>
       <c r="D100" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="E100" s="426"/>
-      <c r="F100" s="358"/>
+      <c r="E100" s="416"/>
+      <c r="F100" s="426"/>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="346"/>
-      <c r="B101" s="367"/>
+      <c r="A101" s="383"/>
+      <c r="B101" s="404"/>
       <c r="C101" s="89" t="s">
         <v>51</v>
       </c>
       <c r="D101" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="E101" s="426"/>
-      <c r="F101" s="358"/>
+      <c r="E101" s="416"/>
+      <c r="F101" s="426"/>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="346"/>
-      <c r="B102" s="367"/>
+      <c r="A102" s="383"/>
+      <c r="B102" s="404"/>
       <c r="C102" s="90" t="s">
         <v>57</v>
       </c>
       <c r="D102" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="E102" s="426"/>
-      <c r="F102" s="359"/>
+      <c r="E102" s="416"/>
+      <c r="F102" s="427"/>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="346"/>
-      <c r="B103" s="348" t="s">
+      <c r="A103" s="383"/>
+      <c r="B103" s="409" t="s">
         <v>36</v>
       </c>
       <c r="C103" s="73" t="s">
@@ -13519,62 +13513,62 @@
         <f>15000000/1000000</f>
         <v>15</v>
       </c>
-      <c r="E103" s="426"/>
-      <c r="F103" s="365" t="s">
+      <c r="E103" s="416"/>
+      <c r="F103" s="390" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="346"/>
-      <c r="B104" s="348"/>
+      <c r="A104" s="383"/>
+      <c r="B104" s="409"/>
       <c r="C104" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D104" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="E104" s="426"/>
-      <c r="F104" s="360"/>
+      <c r="E104" s="416"/>
+      <c r="F104" s="391"/>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="346"/>
-      <c r="B105" s="348"/>
+      <c r="A105" s="383"/>
+      <c r="B105" s="409"/>
       <c r="C105" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D105" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E105" s="426"/>
-      <c r="F105" s="360"/>
+      <c r="E105" s="416"/>
+      <c r="F105" s="391"/>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="346"/>
-      <c r="B106" s="348"/>
+      <c r="A106" s="383"/>
+      <c r="B106" s="409"/>
       <c r="C106" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D106" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="E106" s="426"/>
-      <c r="F106" s="360"/>
+      <c r="E106" s="416"/>
+      <c r="F106" s="391"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="346"/>
-      <c r="B107" s="417"/>
+      <c r="A107" s="383"/>
+      <c r="B107" s="410"/>
       <c r="C107" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D107" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E107" s="426"/>
-      <c r="F107" s="361"/>
+      <c r="E107" s="416"/>
+      <c r="F107" s="392"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="346"/>
-      <c r="B108" s="367" t="s">
+      <c r="A108" s="383"/>
+      <c r="B108" s="404" t="s">
         <v>38</v>
       </c>
       <c r="C108" s="73" t="s">
@@ -13584,62 +13578,62 @@
         <f>30000000/1000000</f>
         <v>30</v>
       </c>
-      <c r="E108" s="426"/>
-      <c r="F108" s="366" t="s">
+      <c r="E108" s="416"/>
+      <c r="F108" s="411" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="346"/>
-      <c r="B109" s="355"/>
+      <c r="A109" s="383"/>
+      <c r="B109" s="403"/>
       <c r="C109" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D109" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="E109" s="426"/>
-      <c r="F109" s="360"/>
+      <c r="E109" s="416"/>
+      <c r="F109" s="391"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="346"/>
-      <c r="B110" s="355"/>
+      <c r="A110" s="383"/>
+      <c r="B110" s="403"/>
       <c r="C110" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D110" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="E110" s="426"/>
-      <c r="F110" s="360"/>
+      <c r="E110" s="416"/>
+      <c r="F110" s="391"/>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="346"/>
-      <c r="B111" s="355"/>
+      <c r="A111" s="383"/>
+      <c r="B111" s="403"/>
       <c r="C111" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D111" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="E111" s="426"/>
-      <c r="F111" s="360"/>
+      <c r="E111" s="416"/>
+      <c r="F111" s="391"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="346"/>
-      <c r="B112" s="355"/>
+      <c r="A112" s="383"/>
+      <c r="B112" s="403"/>
       <c r="C112" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D112" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E112" s="426"/>
-      <c r="F112" s="361"/>
+      <c r="E112" s="416"/>
+      <c r="F112" s="392"/>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="346"/>
-      <c r="B113" s="348" t="s">
+      <c r="A113" s="383"/>
+      <c r="B113" s="409" t="s">
         <v>40</v>
       </c>
       <c r="C113" s="73" t="s">
@@ -13649,94 +13643,94 @@
         <f>2000000/1000000</f>
         <v>2</v>
       </c>
-      <c r="E113" s="426"/>
-      <c r="F113" s="366" t="s">
+      <c r="E113" s="416"/>
+      <c r="F113" s="411" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="346"/>
-      <c r="B114" s="348"/>
+      <c r="A114" s="383"/>
+      <c r="B114" s="409"/>
       <c r="C114" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D114" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E114" s="426"/>
-      <c r="F114" s="360"/>
+      <c r="E114" s="416"/>
+      <c r="F114" s="391"/>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="346"/>
-      <c r="B115" s="348"/>
+      <c r="A115" s="383"/>
+      <c r="B115" s="409"/>
       <c r="C115" s="75" t="s">
         <v>49</v>
       </c>
       <c r="D115" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E115" s="426"/>
-      <c r="F115" s="360"/>
+      <c r="E115" s="416"/>
+      <c r="F115" s="391"/>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="346"/>
-      <c r="B116" s="348"/>
-      <c r="C116" s="377" t="s">
+      <c r="A116" s="383"/>
+      <c r="B116" s="409"/>
+      <c r="C116" s="412" t="s">
         <v>51</v>
       </c>
       <c r="D116" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E116" s="426"/>
-      <c r="F116" s="360"/>
+      <c r="E116" s="416"/>
+      <c r="F116" s="391"/>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="346"/>
-      <c r="B117" s="348"/>
-      <c r="C117" s="378"/>
+      <c r="A117" s="383"/>
+      <c r="B117" s="409"/>
+      <c r="C117" s="413"/>
       <c r="D117" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="E117" s="426"/>
-      <c r="F117" s="360"/>
+      <c r="E117" s="416"/>
+      <c r="F117" s="391"/>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="346"/>
-      <c r="B118" s="348"/>
-      <c r="C118" s="378"/>
+      <c r="A118" s="383"/>
+      <c r="B118" s="409"/>
+      <c r="C118" s="413"/>
       <c r="D118" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="E118" s="426"/>
-      <c r="F118" s="360"/>
+      <c r="E118" s="416"/>
+      <c r="F118" s="391"/>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="346"/>
-      <c r="B119" s="348"/>
-      <c r="C119" s="379"/>
+      <c r="A119" s="383"/>
+      <c r="B119" s="409"/>
+      <c r="C119" s="414"/>
       <c r="D119" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="E119" s="426"/>
-      <c r="F119" s="360"/>
+      <c r="E119" s="416"/>
+      <c r="F119" s="391"/>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="346"/>
-      <c r="B120" s="417"/>
+      <c r="A120" s="383"/>
+      <c r="B120" s="410"/>
       <c r="C120" s="80" t="s">
         <v>57</v>
       </c>
       <c r="D120" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E120" s="428"/>
-      <c r="F120" s="361"/>
+      <c r="E120" s="418"/>
+      <c r="F120" s="392"/>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="346" t="s">
+      <c r="A121" s="383" t="s">
         <v>5</v>
       </c>
-      <c r="B121" s="393" t="s">
+      <c r="B121" s="384" t="s">
         <v>29</v>
       </c>
       <c r="C121" s="66" t="s">
@@ -13746,104 +13740,104 @@
         <f>(9450000+9450000*0.2 + 111780000)/1000000</f>
         <v>123.12</v>
       </c>
-      <c r="E121" s="422" t="s">
+      <c r="E121" s="387" t="s">
         <v>10</v>
       </c>
-      <c r="F121" s="365">
+      <c r="F121" s="390">
         <v>3000</v>
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="346"/>
-      <c r="B122" s="394"/>
+      <c r="A122" s="383"/>
+      <c r="B122" s="385"/>
       <c r="C122" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D122" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E122" s="423"/>
-      <c r="F122" s="360"/>
+      <c r="E122" s="388"/>
+      <c r="F122" s="391"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="346"/>
-      <c r="B123" s="394"/>
+      <c r="A123" s="383"/>
+      <c r="B123" s="385"/>
       <c r="C123" s="63" t="s">
         <v>49</v>
       </c>
       <c r="D123" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E123" s="423"/>
-      <c r="F123" s="360"/>
+      <c r="E123" s="388"/>
+      <c r="F123" s="391"/>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="346"/>
-      <c r="B124" s="394"/>
-      <c r="C124" s="369" t="s">
+      <c r="A124" s="383"/>
+      <c r="B124" s="385"/>
+      <c r="C124" s="432" t="s">
         <v>51</v>
       </c>
       <c r="D124" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="E124" s="423"/>
-      <c r="F124" s="360"/>
+      <c r="E124" s="388"/>
+      <c r="F124" s="391"/>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="346"/>
-      <c r="B125" s="394"/>
-      <c r="C125" s="370"/>
+      <c r="A125" s="383"/>
+      <c r="B125" s="385"/>
+      <c r="C125" s="433"/>
       <c r="D125" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="E125" s="423"/>
-      <c r="F125" s="360"/>
+      <c r="E125" s="388"/>
+      <c r="F125" s="391"/>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="346"/>
-      <c r="B126" s="394"/>
-      <c r="C126" s="370"/>
+      <c r="A126" s="383"/>
+      <c r="B126" s="385"/>
+      <c r="C126" s="433"/>
       <c r="D126" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="E126" s="423"/>
-      <c r="F126" s="360"/>
+      <c r="E126" s="388"/>
+      <c r="F126" s="391"/>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="346"/>
-      <c r="B127" s="394"/>
-      <c r="C127" s="370"/>
+      <c r="A127" s="383"/>
+      <c r="B127" s="385"/>
+      <c r="C127" s="433"/>
       <c r="D127" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="E127" s="423"/>
-      <c r="F127" s="360"/>
+      <c r="E127" s="388"/>
+      <c r="F127" s="391"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="346"/>
-      <c r="B128" s="394"/>
-      <c r="C128" s="370"/>
+      <c r="A128" s="383"/>
+      <c r="B128" s="385"/>
+      <c r="C128" s="433"/>
       <c r="D128" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="E128" s="423"/>
-      <c r="F128" s="360"/>
+      <c r="E128" s="388"/>
+      <c r="F128" s="391"/>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="346"/>
-      <c r="B129" s="394"/>
+      <c r="A129" s="383"/>
+      <c r="B129" s="385"/>
       <c r="C129" s="71" t="s">
         <v>57</v>
       </c>
       <c r="D129" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="E129" s="423"/>
-      <c r="F129" s="361"/>
+      <c r="E129" s="388"/>
+      <c r="F129" s="392"/>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="346"/>
-      <c r="B130" s="351" t="s">
+      <c r="A130" s="383"/>
+      <c r="B130" s="396" t="s">
         <v>32</v>
       </c>
       <c r="C130" s="66" t="s">
@@ -13853,80 +13847,80 @@
         <f>1946099/1000000</f>
         <v>1.946099</v>
       </c>
-      <c r="E130" s="423"/>
-      <c r="F130" s="362"/>
+      <c r="E130" s="388"/>
+      <c r="F130" s="397"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="346"/>
-      <c r="B131" s="351"/>
+      <c r="A131" s="383"/>
+      <c r="B131" s="396"/>
       <c r="C131" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D131" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="E131" s="423"/>
-      <c r="F131" s="363"/>
+      <c r="E131" s="388"/>
+      <c r="F131" s="398"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="346"/>
-      <c r="B132" s="351"/>
+      <c r="A132" s="383"/>
+      <c r="B132" s="396"/>
       <c r="C132" s="71" t="s">
         <v>49</v>
       </c>
       <c r="D132" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="E132" s="423"/>
-      <c r="F132" s="363"/>
+      <c r="E132" s="388"/>
+      <c r="F132" s="398"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="346"/>
-      <c r="B133" s="351"/>
-      <c r="C133" s="352" t="s">
+      <c r="A133" s="383"/>
+      <c r="B133" s="396"/>
+      <c r="C133" s="400" t="s">
         <v>51</v>
       </c>
       <c r="D133" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="E133" s="423"/>
-      <c r="F133" s="363"/>
+      <c r="E133" s="388"/>
+      <c r="F133" s="398"/>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="346"/>
-      <c r="B134" s="351"/>
-      <c r="C134" s="353"/>
+      <c r="A134" s="383"/>
+      <c r="B134" s="396"/>
+      <c r="C134" s="401"/>
       <c r="D134" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="E134" s="423"/>
-      <c r="F134" s="363"/>
+      <c r="E134" s="388"/>
+      <c r="F134" s="398"/>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="346"/>
-      <c r="B135" s="351"/>
-      <c r="C135" s="354"/>
+      <c r="A135" s="383"/>
+      <c r="B135" s="396"/>
+      <c r="C135" s="402"/>
       <c r="D135" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E135" s="423"/>
-      <c r="F135" s="363"/>
+      <c r="E135" s="388"/>
+      <c r="F135" s="398"/>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="346"/>
-      <c r="B136" s="351"/>
+      <c r="A136" s="383"/>
+      <c r="B136" s="396"/>
       <c r="C136" s="72" t="s">
         <v>57</v>
       </c>
       <c r="D136" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E136" s="423"/>
-      <c r="F136" s="364"/>
+      <c r="E136" s="388"/>
+      <c r="F136" s="399"/>
     </row>
     <row r="137" spans="1:6">
-      <c r="A137" s="346"/>
-      <c r="B137" s="355" t="s">
+      <c r="A137" s="383"/>
+      <c r="B137" s="403" t="s">
         <v>34</v>
       </c>
       <c r="C137" s="88" t="s">
@@ -13936,62 +13930,62 @@
         <f>5000000/1000000</f>
         <v>5</v>
       </c>
-      <c r="E137" s="423"/>
-      <c r="F137" s="395" t="s">
+      <c r="E137" s="388"/>
+      <c r="F137" s="406" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="346"/>
-      <c r="B138" s="367"/>
+      <c r="A138" s="383"/>
+      <c r="B138" s="404"/>
       <c r="C138" s="89" t="s">
         <v>47</v>
       </c>
       <c r="D138" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="E138" s="423"/>
-      <c r="F138" s="396"/>
+      <c r="E138" s="388"/>
+      <c r="F138" s="407"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="A139" s="346"/>
-      <c r="B139" s="367"/>
+      <c r="A139" s="383"/>
+      <c r="B139" s="404"/>
       <c r="C139" s="89" t="s">
         <v>49</v>
       </c>
       <c r="D139" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="E139" s="423"/>
-      <c r="F139" s="396"/>
+      <c r="E139" s="388"/>
+      <c r="F139" s="407"/>
     </row>
     <row r="140" spans="1:6">
-      <c r="A140" s="346"/>
-      <c r="B140" s="367"/>
+      <c r="A140" s="383"/>
+      <c r="B140" s="404"/>
       <c r="C140" s="89" t="s">
         <v>51</v>
       </c>
       <c r="D140" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="E140" s="423"/>
-      <c r="F140" s="396"/>
+      <c r="E140" s="388"/>
+      <c r="F140" s="407"/>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="346"/>
-      <c r="B141" s="367"/>
+      <c r="A141" s="383"/>
+      <c r="B141" s="404"/>
       <c r="C141" s="90" t="s">
         <v>57</v>
       </c>
       <c r="D141" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="E141" s="423"/>
-      <c r="F141" s="397"/>
+      <c r="E141" s="388"/>
+      <c r="F141" s="408"/>
     </row>
     <row r="142" spans="1:6">
-      <c r="A142" s="346"/>
-      <c r="B142" s="348" t="s">
+      <c r="A142" s="383"/>
+      <c r="B142" s="409" t="s">
         <v>36</v>
       </c>
       <c r="C142" s="73" t="s">
@@ -14001,62 +13995,62 @@
         <f>20000000/1000000</f>
         <v>20</v>
       </c>
-      <c r="E142" s="423"/>
-      <c r="F142" s="365" t="s">
+      <c r="E142" s="388"/>
+      <c r="F142" s="390" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:6">
-      <c r="A143" s="346"/>
-      <c r="B143" s="348"/>
+      <c r="A143" s="383"/>
+      <c r="B143" s="409"/>
       <c r="C143" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D143" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="423"/>
-      <c r="F143" s="360"/>
+      <c r="E143" s="388"/>
+      <c r="F143" s="391"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="346"/>
-      <c r="B144" s="348"/>
+      <c r="A144" s="383"/>
+      <c r="B144" s="409"/>
       <c r="C144" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D144" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E144" s="423"/>
-      <c r="F144" s="360"/>
+      <c r="E144" s="388"/>
+      <c r="F144" s="391"/>
     </row>
     <row r="145" spans="1:6">
-      <c r="A145" s="346"/>
-      <c r="B145" s="348"/>
+      <c r="A145" s="383"/>
+      <c r="B145" s="409"/>
       <c r="C145" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D145" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="E145" s="423"/>
-      <c r="F145" s="360"/>
+      <c r="E145" s="388"/>
+      <c r="F145" s="391"/>
     </row>
     <row r="146" spans="1:6">
-      <c r="A146" s="346"/>
-      <c r="B146" s="417"/>
+      <c r="A146" s="383"/>
+      <c r="B146" s="410"/>
       <c r="C146" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D146" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E146" s="423"/>
-      <c r="F146" s="361"/>
+      <c r="E146" s="388"/>
+      <c r="F146" s="392"/>
     </row>
     <row r="147" spans="1:6">
-      <c r="A147" s="346"/>
-      <c r="B147" s="367" t="s">
+      <c r="A147" s="383"/>
+      <c r="B147" s="404" t="s">
         <v>38</v>
       </c>
       <c r="C147" s="73" t="s">
@@ -14066,62 +14060,62 @@
         <f>31000000/1000000</f>
         <v>31</v>
       </c>
-      <c r="E147" s="423"/>
-      <c r="F147" s="366" t="s">
+      <c r="E147" s="388"/>
+      <c r="F147" s="411" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:6">
-      <c r="A148" s="346"/>
-      <c r="B148" s="355"/>
+      <c r="A148" s="383"/>
+      <c r="B148" s="403"/>
       <c r="C148" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D148" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="E148" s="423"/>
-      <c r="F148" s="360"/>
+      <c r="E148" s="388"/>
+      <c r="F148" s="391"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="A149" s="346"/>
-      <c r="B149" s="355"/>
+      <c r="A149" s="383"/>
+      <c r="B149" s="403"/>
       <c r="C149" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D149" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="E149" s="423"/>
-      <c r="F149" s="360"/>
+      <c r="E149" s="388"/>
+      <c r="F149" s="391"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="A150" s="346"/>
-      <c r="B150" s="355"/>
+      <c r="A150" s="383"/>
+      <c r="B150" s="403"/>
       <c r="C150" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D150" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="E150" s="423"/>
-      <c r="F150" s="360"/>
+      <c r="E150" s="388"/>
+      <c r="F150" s="391"/>
     </row>
     <row r="151" spans="1:6">
-      <c r="A151" s="346"/>
-      <c r="B151" s="356"/>
+      <c r="A151" s="383"/>
+      <c r="B151" s="421"/>
       <c r="C151" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D151" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E151" s="423"/>
-      <c r="F151" s="361"/>
+      <c r="E151" s="388"/>
+      <c r="F151" s="392"/>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" s="346"/>
-      <c r="B152" s="347" t="s">
+      <c r="A152" s="383"/>
+      <c r="B152" s="431" t="s">
         <v>40</v>
       </c>
       <c r="C152" s="73" t="s">
@@ -14131,94 +14125,94 @@
         <f>4000000/1000000</f>
         <v>4</v>
       </c>
-      <c r="E152" s="423"/>
-      <c r="F152" s="366" t="s">
+      <c r="E152" s="388"/>
+      <c r="F152" s="411" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="153" spans="1:6">
-      <c r="A153" s="346"/>
-      <c r="B153" s="348"/>
+      <c r="A153" s="383"/>
+      <c r="B153" s="409"/>
       <c r="C153" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D153" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E153" s="423"/>
-      <c r="F153" s="360"/>
+      <c r="E153" s="388"/>
+      <c r="F153" s="391"/>
     </row>
     <row r="154" spans="1:6">
-      <c r="A154" s="346"/>
-      <c r="B154" s="348"/>
+      <c r="A154" s="383"/>
+      <c r="B154" s="409"/>
       <c r="C154" s="75" t="s">
         <v>49</v>
       </c>
       <c r="D154" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E154" s="423"/>
-      <c r="F154" s="360"/>
+      <c r="E154" s="388"/>
+      <c r="F154" s="391"/>
     </row>
     <row r="155" spans="1:6">
-      <c r="A155" s="346"/>
-      <c r="B155" s="348"/>
-      <c r="C155" s="377" t="s">
+      <c r="A155" s="383"/>
+      <c r="B155" s="409"/>
+      <c r="C155" s="412" t="s">
         <v>51</v>
       </c>
       <c r="D155" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E155" s="423"/>
-      <c r="F155" s="360"/>
+      <c r="E155" s="388"/>
+      <c r="F155" s="391"/>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="346"/>
-      <c r="B156" s="348"/>
-      <c r="C156" s="378"/>
+      <c r="A156" s="383"/>
+      <c r="B156" s="409"/>
+      <c r="C156" s="413"/>
       <c r="D156" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="E156" s="423"/>
-      <c r="F156" s="360"/>
+      <c r="E156" s="388"/>
+      <c r="F156" s="391"/>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="346"/>
-      <c r="B157" s="348"/>
-      <c r="C157" s="378"/>
+      <c r="A157" s="383"/>
+      <c r="B157" s="409"/>
+      <c r="C157" s="413"/>
       <c r="D157" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="E157" s="423"/>
-      <c r="F157" s="360"/>
+      <c r="E157" s="388"/>
+      <c r="F157" s="391"/>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="346"/>
-      <c r="B158" s="348"/>
-      <c r="C158" s="379"/>
+      <c r="A158" s="383"/>
+      <c r="B158" s="409"/>
+      <c r="C158" s="414"/>
       <c r="D158" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="E158" s="423"/>
-      <c r="F158" s="360"/>
+      <c r="E158" s="388"/>
+      <c r="F158" s="391"/>
     </row>
     <row r="159" spans="1:6">
-      <c r="A159" s="346"/>
-      <c r="B159" s="417"/>
+      <c r="A159" s="383"/>
+      <c r="B159" s="410"/>
       <c r="C159" s="80" t="s">
         <v>57</v>
       </c>
       <c r="D159" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E159" s="424"/>
-      <c r="F159" s="361"/>
+      <c r="E159" s="389"/>
+      <c r="F159" s="392"/>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="346" t="s">
+      <c r="A160" s="383" t="s">
         <v>6</v>
       </c>
-      <c r="B160" s="393" t="s">
+      <c r="B160" s="384" t="s">
         <v>29</v>
       </c>
       <c r="C160" s="66" t="s">
@@ -14228,104 +14222,104 @@
         <f>(9450000+9450000*0.5+141020000)/1000000</f>
         <v>155.19499999999999</v>
       </c>
-      <c r="E160" s="434" t="s">
+      <c r="E160" s="428" t="s">
         <v>10</v>
       </c>
-      <c r="F160" s="365">
+      <c r="F160" s="390">
         <v>3800</v>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="A161" s="346"/>
-      <c r="B161" s="394"/>
+      <c r="A161" s="383"/>
+      <c r="B161" s="385"/>
       <c r="C161" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D161" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E161" s="435"/>
-      <c r="F161" s="360"/>
+      <c r="E161" s="429"/>
+      <c r="F161" s="391"/>
     </row>
     <row r="162" spans="1:6">
-      <c r="A162" s="346"/>
-      <c r="B162" s="394"/>
+      <c r="A162" s="383"/>
+      <c r="B162" s="385"/>
       <c r="C162" s="71" t="s">
         <v>49</v>
       </c>
       <c r="D162" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E162" s="435"/>
-      <c r="F162" s="360"/>
+      <c r="E162" s="429"/>
+      <c r="F162" s="391"/>
     </row>
     <row r="163" spans="1:6">
-      <c r="A163" s="346"/>
-      <c r="B163" s="418"/>
-      <c r="C163" s="419" t="s">
+      <c r="A163" s="383"/>
+      <c r="B163" s="386"/>
+      <c r="C163" s="393" t="s">
         <v>51</v>
       </c>
       <c r="D163" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="E163" s="435"/>
-      <c r="F163" s="360"/>
+      <c r="E163" s="429"/>
+      <c r="F163" s="391"/>
     </row>
     <row r="164" spans="1:6">
-      <c r="A164" s="346"/>
-      <c r="B164" s="418"/>
-      <c r="C164" s="420"/>
+      <c r="A164" s="383"/>
+      <c r="B164" s="386"/>
+      <c r="C164" s="394"/>
       <c r="D164" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="E164" s="435"/>
-      <c r="F164" s="360"/>
+      <c r="E164" s="429"/>
+      <c r="F164" s="391"/>
     </row>
     <row r="165" spans="1:6">
-      <c r="A165" s="346"/>
-      <c r="B165" s="418"/>
-      <c r="C165" s="420"/>
+      <c r="A165" s="383"/>
+      <c r="B165" s="386"/>
+      <c r="C165" s="394"/>
       <c r="D165" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="E165" s="435"/>
-      <c r="F165" s="360"/>
+      <c r="E165" s="429"/>
+      <c r="F165" s="391"/>
     </row>
     <row r="166" spans="1:6">
-      <c r="A166" s="346"/>
-      <c r="B166" s="418"/>
-      <c r="C166" s="420"/>
+      <c r="A166" s="383"/>
+      <c r="B166" s="386"/>
+      <c r="C166" s="394"/>
       <c r="D166" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="E166" s="435"/>
-      <c r="F166" s="360"/>
+      <c r="E166" s="429"/>
+      <c r="F166" s="391"/>
     </row>
     <row r="167" spans="1:6">
-      <c r="A167" s="346"/>
-      <c r="B167" s="418"/>
-      <c r="C167" s="421"/>
+      <c r="A167" s="383"/>
+      <c r="B167" s="386"/>
+      <c r="C167" s="395"/>
       <c r="D167" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="E167" s="435"/>
-      <c r="F167" s="360"/>
+      <c r="E167" s="429"/>
+      <c r="F167" s="391"/>
     </row>
     <row r="168" spans="1:6">
-      <c r="A168" s="346"/>
-      <c r="B168" s="394"/>
+      <c r="A168" s="383"/>
+      <c r="B168" s="385"/>
       <c r="C168" s="122" t="s">
         <v>57</v>
       </c>
       <c r="D168" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="E168" s="435"/>
-      <c r="F168" s="361"/>
+      <c r="E168" s="429"/>
+      <c r="F168" s="392"/>
     </row>
     <row r="169" spans="1:6">
-      <c r="A169" s="346"/>
-      <c r="B169" s="351" t="s">
+      <c r="A169" s="383"/>
+      <c r="B169" s="396" t="s">
         <v>32</v>
       </c>
       <c r="C169" s="66" t="s">
@@ -14335,80 +14329,80 @@
         <f>23600000/1000000</f>
         <v>23.6</v>
       </c>
-      <c r="E169" s="435"/>
-      <c r="F169" s="362"/>
+      <c r="E169" s="429"/>
+      <c r="F169" s="397"/>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="346"/>
-      <c r="B170" s="351"/>
+      <c r="A170" s="383"/>
+      <c r="B170" s="396"/>
       <c r="C170" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D170" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="E170" s="435"/>
-      <c r="F170" s="363"/>
+      <c r="E170" s="429"/>
+      <c r="F170" s="398"/>
     </row>
     <row r="171" spans="1:6">
-      <c r="A171" s="346"/>
-      <c r="B171" s="351"/>
+      <c r="A171" s="383"/>
+      <c r="B171" s="396"/>
       <c r="C171" s="71" t="s">
         <v>49</v>
       </c>
       <c r="D171" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="E171" s="435"/>
-      <c r="F171" s="363"/>
+      <c r="E171" s="429"/>
+      <c r="F171" s="398"/>
     </row>
     <row r="172" spans="1:6">
-      <c r="A172" s="346"/>
-      <c r="B172" s="351"/>
-      <c r="C172" s="352" t="s">
+      <c r="A172" s="383"/>
+      <c r="B172" s="396"/>
+      <c r="C172" s="400" t="s">
         <v>51</v>
       </c>
       <c r="D172" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="E172" s="435"/>
-      <c r="F172" s="363"/>
+      <c r="E172" s="429"/>
+      <c r="F172" s="398"/>
     </row>
     <row r="173" spans="1:6">
-      <c r="A173" s="346"/>
-      <c r="B173" s="351"/>
-      <c r="C173" s="353"/>
+      <c r="A173" s="383"/>
+      <c r="B173" s="396"/>
+      <c r="C173" s="401"/>
       <c r="D173" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="E173" s="435"/>
-      <c r="F173" s="363"/>
+      <c r="E173" s="429"/>
+      <c r="F173" s="398"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="A174" s="346"/>
-      <c r="B174" s="351"/>
-      <c r="C174" s="354"/>
+      <c r="A174" s="383"/>
+      <c r="B174" s="396"/>
+      <c r="C174" s="402"/>
       <c r="D174" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E174" s="435"/>
-      <c r="F174" s="363"/>
+      <c r="E174" s="429"/>
+      <c r="F174" s="398"/>
     </row>
     <row r="175" spans="1:6">
-      <c r="A175" s="346"/>
-      <c r="B175" s="351"/>
+      <c r="A175" s="383"/>
+      <c r="B175" s="396"/>
       <c r="C175" s="72" t="s">
         <v>57</v>
       </c>
       <c r="D175" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E175" s="435"/>
-      <c r="F175" s="364"/>
+      <c r="E175" s="429"/>
+      <c r="F175" s="399"/>
     </row>
     <row r="176" spans="1:6">
-      <c r="A176" s="346"/>
-      <c r="B176" s="355" t="s">
+      <c r="A176" s="383"/>
+      <c r="B176" s="403" t="s">
         <v>34</v>
       </c>
       <c r="C176" s="88" t="s">
@@ -14418,62 +14412,62 @@
         <f>30000000/1000000</f>
         <v>30</v>
       </c>
-      <c r="E176" s="435"/>
-      <c r="F176" s="395">
+      <c r="E176" s="429"/>
+      <c r="F176" s="406">
         <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:6">
-      <c r="A177" s="346"/>
-      <c r="B177" s="367"/>
+      <c r="A177" s="383"/>
+      <c r="B177" s="404"/>
       <c r="C177" s="89" t="s">
         <v>47</v>
       </c>
       <c r="D177" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="E177" s="435"/>
-      <c r="F177" s="396"/>
+      <c r="E177" s="429"/>
+      <c r="F177" s="407"/>
     </row>
     <row r="178" spans="1:6">
-      <c r="A178" s="346"/>
-      <c r="B178" s="367"/>
+      <c r="A178" s="383"/>
+      <c r="B178" s="404"/>
       <c r="C178" s="89" t="s">
         <v>49</v>
       </c>
       <c r="D178" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="E178" s="435"/>
-      <c r="F178" s="396"/>
+      <c r="E178" s="429"/>
+      <c r="F178" s="407"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="A179" s="346"/>
-      <c r="B179" s="367"/>
+      <c r="A179" s="383"/>
+      <c r="B179" s="404"/>
       <c r="C179" s="89" t="s">
         <v>51</v>
       </c>
       <c r="D179" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="E179" s="435"/>
-      <c r="F179" s="396"/>
+      <c r="E179" s="429"/>
+      <c r="F179" s="407"/>
     </row>
     <row r="180" spans="1:6">
-      <c r="A180" s="346"/>
-      <c r="B180" s="368"/>
+      <c r="A180" s="383"/>
+      <c r="B180" s="405"/>
       <c r="C180" s="90" t="s">
         <v>57</v>
       </c>
       <c r="D180" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="E180" s="435"/>
-      <c r="F180" s="397"/>
+      <c r="E180" s="429"/>
+      <c r="F180" s="408"/>
     </row>
     <row r="181" spans="1:6">
-      <c r="A181" s="346"/>
-      <c r="B181" s="393" t="s">
+      <c r="A181" s="383"/>
+      <c r="B181" s="384" t="s">
         <v>36</v>
       </c>
       <c r="C181" s="66" t="s">
@@ -14483,62 +14477,62 @@
         <f>150000000/1000000</f>
         <v>150</v>
       </c>
-      <c r="E181" s="435"/>
-      <c r="F181" s="365" t="s">
+      <c r="E181" s="429"/>
+      <c r="F181" s="390" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="A182" s="346"/>
-      <c r="B182" s="394"/>
+      <c r="A182" s="383"/>
+      <c r="B182" s="385"/>
       <c r="C182" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D182" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="E182" s="435"/>
-      <c r="F182" s="360"/>
+      <c r="E182" s="429"/>
+      <c r="F182" s="391"/>
     </row>
     <row r="183" spans="1:6">
-      <c r="A183" s="346"/>
-      <c r="B183" s="394"/>
+      <c r="A183" s="383"/>
+      <c r="B183" s="385"/>
       <c r="C183" s="63" t="s">
         <v>49</v>
       </c>
       <c r="D183" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E183" s="435"/>
-      <c r="F183" s="360"/>
+      <c r="E183" s="429"/>
+      <c r="F183" s="391"/>
     </row>
     <row r="184" spans="1:6">
-      <c r="A184" s="346"/>
-      <c r="B184" s="394"/>
+      <c r="A184" s="383"/>
+      <c r="B184" s="385"/>
       <c r="C184" s="63" t="s">
         <v>51</v>
       </c>
       <c r="D184" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="E184" s="435"/>
-      <c r="F184" s="360"/>
+      <c r="E184" s="429"/>
+      <c r="F184" s="391"/>
     </row>
     <row r="185" spans="1:6">
-      <c r="A185" s="346"/>
-      <c r="B185" s="394"/>
+      <c r="A185" s="383"/>
+      <c r="B185" s="385"/>
       <c r="C185" s="67" t="s">
         <v>57</v>
       </c>
       <c r="D185" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E185" s="435"/>
-      <c r="F185" s="361"/>
+      <c r="E185" s="429"/>
+      <c r="F185" s="392"/>
     </row>
     <row r="186" spans="1:6">
-      <c r="A186" s="346"/>
-      <c r="B186" s="355" t="s">
+      <c r="A186" s="383"/>
+      <c r="B186" s="403" t="s">
         <v>38</v>
       </c>
       <c r="C186" s="73" t="s">
@@ -14548,62 +14542,62 @@
         <f>60000000/1000000</f>
         <v>60</v>
       </c>
-      <c r="E186" s="435"/>
-      <c r="F186" s="366" t="s">
+      <c r="E186" s="429"/>
+      <c r="F186" s="411" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:6">
-      <c r="A187" s="346"/>
-      <c r="B187" s="355"/>
+      <c r="A187" s="383"/>
+      <c r="B187" s="403"/>
       <c r="C187" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D187" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="E187" s="435"/>
-      <c r="F187" s="360"/>
+      <c r="E187" s="429"/>
+      <c r="F187" s="391"/>
     </row>
     <row r="188" spans="1:6">
-      <c r="A188" s="346"/>
-      <c r="B188" s="355"/>
+      <c r="A188" s="383"/>
+      <c r="B188" s="403"/>
       <c r="C188" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D188" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="E188" s="435"/>
-      <c r="F188" s="360"/>
+      <c r="E188" s="429"/>
+      <c r="F188" s="391"/>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="346"/>
-      <c r="B189" s="355"/>
+      <c r="A189" s="383"/>
+      <c r="B189" s="403"/>
       <c r="C189" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D189" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="E189" s="435"/>
-      <c r="F189" s="360"/>
+      <c r="E189" s="429"/>
+      <c r="F189" s="391"/>
     </row>
     <row r="190" spans="1:6">
-      <c r="A190" s="346"/>
-      <c r="B190" s="355"/>
+      <c r="A190" s="383"/>
+      <c r="B190" s="403"/>
       <c r="C190" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D190" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E190" s="435"/>
-      <c r="F190" s="361"/>
+      <c r="E190" s="429"/>
+      <c r="F190" s="392"/>
     </row>
     <row r="191" spans="1:6">
-      <c r="A191" s="346"/>
-      <c r="B191" s="348" t="s">
+      <c r="A191" s="383"/>
+      <c r="B191" s="409" t="s">
         <v>40</v>
       </c>
       <c r="C191" s="73" t="s">
@@ -14613,94 +14607,94 @@
         <f>40000000/1000000</f>
         <v>40</v>
       </c>
-      <c r="E191" s="435"/>
-      <c r="F191" s="366">
+      <c r="E191" s="429"/>
+      <c r="F191" s="411">
         <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:6">
-      <c r="A192" s="346"/>
-      <c r="B192" s="348"/>
+      <c r="A192" s="383"/>
+      <c r="B192" s="409"/>
       <c r="C192" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D192" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E192" s="435"/>
-      <c r="F192" s="360"/>
+      <c r="E192" s="429"/>
+      <c r="F192" s="391"/>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="346"/>
-      <c r="B193" s="348"/>
+      <c r="A193" s="383"/>
+      <c r="B193" s="409"/>
       <c r="C193" s="75" t="s">
         <v>49</v>
       </c>
       <c r="D193" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E193" s="435"/>
-      <c r="F193" s="360"/>
+      <c r="E193" s="429"/>
+      <c r="F193" s="391"/>
     </row>
     <row r="194" spans="1:6">
-      <c r="A194" s="346"/>
-      <c r="B194" s="348"/>
-      <c r="C194" s="377" t="s">
+      <c r="A194" s="383"/>
+      <c r="B194" s="409"/>
+      <c r="C194" s="412" t="s">
         <v>51</v>
       </c>
       <c r="D194" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E194" s="435"/>
-      <c r="F194" s="360"/>
+      <c r="E194" s="429"/>
+      <c r="F194" s="391"/>
     </row>
     <row r="195" spans="1:6">
-      <c r="A195" s="346"/>
-      <c r="B195" s="348"/>
-      <c r="C195" s="378"/>
+      <c r="A195" s="383"/>
+      <c r="B195" s="409"/>
+      <c r="C195" s="413"/>
       <c r="D195" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="E195" s="435"/>
-      <c r="F195" s="360"/>
+      <c r="E195" s="429"/>
+      <c r="F195" s="391"/>
     </row>
     <row r="196" spans="1:6">
-      <c r="A196" s="346"/>
-      <c r="B196" s="348"/>
-      <c r="C196" s="378"/>
+      <c r="A196" s="383"/>
+      <c r="B196" s="409"/>
+      <c r="C196" s="413"/>
       <c r="D196" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="E196" s="435"/>
-      <c r="F196" s="360"/>
+      <c r="E196" s="429"/>
+      <c r="F196" s="391"/>
     </row>
     <row r="197" spans="1:6">
-      <c r="A197" s="346"/>
-      <c r="B197" s="348"/>
-      <c r="C197" s="379"/>
+      <c r="A197" s="383"/>
+      <c r="B197" s="409"/>
+      <c r="C197" s="414"/>
       <c r="D197" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="E197" s="435"/>
-      <c r="F197" s="360"/>
+      <c r="E197" s="429"/>
+      <c r="F197" s="391"/>
     </row>
     <row r="198" spans="1:6">
-      <c r="A198" s="346"/>
-      <c r="B198" s="417"/>
+      <c r="A198" s="383"/>
+      <c r="B198" s="410"/>
       <c r="C198" s="80" t="s">
         <v>57</v>
       </c>
       <c r="D198" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E198" s="436"/>
-      <c r="F198" s="361"/>
+      <c r="E198" s="430"/>
+      <c r="F198" s="392"/>
     </row>
     <row r="199" spans="1:6">
-      <c r="A199" s="346" t="s">
+      <c r="A199" s="383" t="s">
         <v>7</v>
       </c>
-      <c r="B199" s="393" t="s">
+      <c r="B199" s="384" t="s">
         <v>29</v>
       </c>
       <c r="C199" s="66" t="s">
@@ -14710,104 +14704,104 @@
         <f>(9450000+9450000*0.8+216740000)/1000000</f>
         <v>233.75</v>
       </c>
-      <c r="E199" s="422" t="s">
+      <c r="E199" s="387" t="s">
         <v>83</v>
       </c>
-      <c r="F199" s="365">
+      <c r="F199" s="390">
         <v>4500</v>
       </c>
     </row>
     <row r="200" spans="1:6">
-      <c r="A200" s="346"/>
-      <c r="B200" s="394"/>
+      <c r="A200" s="383"/>
+      <c r="B200" s="385"/>
       <c r="C200" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D200" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E200" s="423"/>
-      <c r="F200" s="360"/>
+      <c r="E200" s="388"/>
+      <c r="F200" s="391"/>
     </row>
     <row r="201" spans="1:6">
-      <c r="A201" s="346"/>
-      <c r="B201" s="394"/>
+      <c r="A201" s="383"/>
+      <c r="B201" s="385"/>
       <c r="C201" s="71" t="s">
         <v>49</v>
       </c>
       <c r="D201" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E201" s="423"/>
-      <c r="F201" s="360"/>
+      <c r="E201" s="388"/>
+      <c r="F201" s="391"/>
     </row>
     <row r="202" spans="1:6">
-      <c r="A202" s="346"/>
-      <c r="B202" s="418"/>
-      <c r="C202" s="419" t="s">
+      <c r="A202" s="383"/>
+      <c r="B202" s="386"/>
+      <c r="C202" s="393" t="s">
         <v>51</v>
       </c>
       <c r="D202" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="E202" s="423"/>
-      <c r="F202" s="360"/>
+      <c r="E202" s="388"/>
+      <c r="F202" s="391"/>
     </row>
     <row r="203" spans="1:6">
-      <c r="A203" s="346"/>
-      <c r="B203" s="418"/>
-      <c r="C203" s="420"/>
+      <c r="A203" s="383"/>
+      <c r="B203" s="386"/>
+      <c r="C203" s="394"/>
       <c r="D203" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="E203" s="423"/>
-      <c r="F203" s="360"/>
+      <c r="E203" s="388"/>
+      <c r="F203" s="391"/>
     </row>
     <row r="204" spans="1:6">
-      <c r="A204" s="346"/>
-      <c r="B204" s="418"/>
-      <c r="C204" s="420"/>
+      <c r="A204" s="383"/>
+      <c r="B204" s="386"/>
+      <c r="C204" s="394"/>
       <c r="D204" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="E204" s="423"/>
-      <c r="F204" s="360"/>
+      <c r="E204" s="388"/>
+      <c r="F204" s="391"/>
     </row>
     <row r="205" spans="1:6">
-      <c r="A205" s="346"/>
-      <c r="B205" s="418"/>
-      <c r="C205" s="420"/>
+      <c r="A205" s="383"/>
+      <c r="B205" s="386"/>
+      <c r="C205" s="394"/>
       <c r="D205" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="E205" s="423"/>
-      <c r="F205" s="360"/>
+      <c r="E205" s="388"/>
+      <c r="F205" s="391"/>
     </row>
     <row r="206" spans="1:6">
-      <c r="A206" s="346"/>
-      <c r="B206" s="418"/>
-      <c r="C206" s="421"/>
+      <c r="A206" s="383"/>
+      <c r="B206" s="386"/>
+      <c r="C206" s="395"/>
       <c r="D206" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="E206" s="423"/>
-      <c r="F206" s="360"/>
+      <c r="E206" s="388"/>
+      <c r="F206" s="391"/>
     </row>
     <row r="207" spans="1:6">
-      <c r="A207" s="346"/>
-      <c r="B207" s="394"/>
+      <c r="A207" s="383"/>
+      <c r="B207" s="385"/>
       <c r="C207" s="122" t="s">
         <v>57</v>
       </c>
       <c r="D207" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="E207" s="423"/>
-      <c r="F207" s="361"/>
+      <c r="E207" s="388"/>
+      <c r="F207" s="392"/>
     </row>
     <row r="208" spans="1:6">
-      <c r="A208" s="346"/>
-      <c r="B208" s="351" t="s">
+      <c r="A208" s="383"/>
+      <c r="B208" s="396" t="s">
         <v>32</v>
       </c>
       <c r="C208" s="66" t="s">
@@ -14817,80 +14811,80 @@
         <f>45360000/1000000</f>
         <v>45.36</v>
       </c>
-      <c r="E208" s="423"/>
-      <c r="F208" s="362"/>
+      <c r="E208" s="388"/>
+      <c r="F208" s="397"/>
     </row>
     <row r="209" spans="1:6">
-      <c r="A209" s="346"/>
-      <c r="B209" s="351"/>
+      <c r="A209" s="383"/>
+      <c r="B209" s="396"/>
       <c r="C209" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D209" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="E209" s="423"/>
-      <c r="F209" s="363"/>
+      <c r="E209" s="388"/>
+      <c r="F209" s="398"/>
     </row>
     <row r="210" spans="1:6">
-      <c r="A210" s="346"/>
-      <c r="B210" s="351"/>
+      <c r="A210" s="383"/>
+      <c r="B210" s="396"/>
       <c r="C210" s="71" t="s">
         <v>49</v>
       </c>
       <c r="D210" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="E210" s="423"/>
-      <c r="F210" s="363"/>
+      <c r="E210" s="388"/>
+      <c r="F210" s="398"/>
     </row>
     <row r="211" spans="1:6">
-      <c r="A211" s="346"/>
-      <c r="B211" s="351"/>
-      <c r="C211" s="352" t="s">
+      <c r="A211" s="383"/>
+      <c r="B211" s="396"/>
+      <c r="C211" s="400" t="s">
         <v>51</v>
       </c>
       <c r="D211" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="E211" s="423"/>
-      <c r="F211" s="363"/>
+      <c r="E211" s="388"/>
+      <c r="F211" s="398"/>
     </row>
     <row r="212" spans="1:6">
-      <c r="A212" s="346"/>
-      <c r="B212" s="351"/>
-      <c r="C212" s="353"/>
+      <c r="A212" s="383"/>
+      <c r="B212" s="396"/>
+      <c r="C212" s="401"/>
       <c r="D212" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="E212" s="423"/>
-      <c r="F212" s="363"/>
+      <c r="E212" s="388"/>
+      <c r="F212" s="398"/>
     </row>
     <row r="213" spans="1:6">
-      <c r="A213" s="346"/>
-      <c r="B213" s="351"/>
-      <c r="C213" s="354"/>
+      <c r="A213" s="383"/>
+      <c r="B213" s="396"/>
+      <c r="C213" s="402"/>
       <c r="D213" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="E213" s="423"/>
-      <c r="F213" s="363"/>
+      <c r="E213" s="388"/>
+      <c r="F213" s="398"/>
     </row>
     <row r="214" spans="1:6">
-      <c r="A214" s="346"/>
-      <c r="B214" s="351"/>
+      <c r="A214" s="383"/>
+      <c r="B214" s="396"/>
       <c r="C214" s="72" t="s">
         <v>57</v>
       </c>
       <c r="D214" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E214" s="423"/>
-      <c r="F214" s="364"/>
+      <c r="E214" s="388"/>
+      <c r="F214" s="399"/>
     </row>
     <row r="215" spans="1:6">
-      <c r="A215" s="346"/>
-      <c r="B215" s="355" t="s">
+      <c r="A215" s="383"/>
+      <c r="B215" s="403" t="s">
         <v>34</v>
       </c>
       <c r="C215" s="88" t="s">
@@ -14900,62 +14894,62 @@
         <f>60000000/1000000</f>
         <v>60</v>
       </c>
-      <c r="E215" s="423"/>
-      <c r="F215" s="395">
+      <c r="E215" s="388"/>
+      <c r="F215" s="406">
         <v>30</v>
       </c>
     </row>
     <row r="216" spans="1:6">
-      <c r="A216" s="346"/>
-      <c r="B216" s="367"/>
+      <c r="A216" s="383"/>
+      <c r="B216" s="404"/>
       <c r="C216" s="89" t="s">
         <v>47</v>
       </c>
       <c r="D216" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="E216" s="423"/>
-      <c r="F216" s="396"/>
+      <c r="E216" s="388"/>
+      <c r="F216" s="407"/>
     </row>
     <row r="217" spans="1:6">
-      <c r="A217" s="346"/>
-      <c r="B217" s="367"/>
+      <c r="A217" s="383"/>
+      <c r="B217" s="404"/>
       <c r="C217" s="89" t="s">
         <v>49</v>
       </c>
       <c r="D217" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="E217" s="423"/>
-      <c r="F217" s="396"/>
+      <c r="E217" s="388"/>
+      <c r="F217" s="407"/>
     </row>
     <row r="218" spans="1:6">
-      <c r="A218" s="346"/>
-      <c r="B218" s="367"/>
+      <c r="A218" s="383"/>
+      <c r="B218" s="404"/>
       <c r="C218" s="89" t="s">
         <v>51</v>
       </c>
       <c r="D218" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="E218" s="423"/>
-      <c r="F218" s="396"/>
+      <c r="E218" s="388"/>
+      <c r="F218" s="407"/>
     </row>
     <row r="219" spans="1:6">
-      <c r="A219" s="346"/>
-      <c r="B219" s="368"/>
+      <c r="A219" s="383"/>
+      <c r="B219" s="405"/>
       <c r="C219" s="90" t="s">
         <v>57</v>
       </c>
       <c r="D219" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="E219" s="423"/>
-      <c r="F219" s="397"/>
+      <c r="E219" s="388"/>
+      <c r="F219" s="408"/>
     </row>
     <row r="220" spans="1:6">
-      <c r="A220" s="346"/>
-      <c r="B220" s="393" t="s">
+      <c r="A220" s="383"/>
+      <c r="B220" s="384" t="s">
         <v>36</v>
       </c>
       <c r="C220" s="66" t="s">
@@ -14965,62 +14959,62 @@
         <f>300000000/1000000</f>
         <v>300</v>
       </c>
-      <c r="E220" s="423"/>
-      <c r="F220" s="365" t="s">
+      <c r="E220" s="388"/>
+      <c r="F220" s="390" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="221" spans="1:6">
-      <c r="A221" s="346"/>
-      <c r="B221" s="394"/>
+      <c r="A221" s="383"/>
+      <c r="B221" s="385"/>
       <c r="C221" s="63" t="s">
         <v>47</v>
       </c>
       <c r="D221" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="E221" s="423"/>
-      <c r="F221" s="360"/>
+      <c r="E221" s="388"/>
+      <c r="F221" s="391"/>
     </row>
     <row r="222" spans="1:6">
-      <c r="A222" s="346"/>
-      <c r="B222" s="394"/>
+      <c r="A222" s="383"/>
+      <c r="B222" s="385"/>
       <c r="C222" s="63" t="s">
         <v>49</v>
       </c>
       <c r="D222" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E222" s="423"/>
-      <c r="F222" s="360"/>
+      <c r="E222" s="388"/>
+      <c r="F222" s="391"/>
     </row>
     <row r="223" spans="1:6">
-      <c r="A223" s="346"/>
-      <c r="B223" s="394"/>
+      <c r="A223" s="383"/>
+      <c r="B223" s="385"/>
       <c r="C223" s="63" t="s">
         <v>51</v>
       </c>
       <c r="D223" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="E223" s="423"/>
-      <c r="F223" s="360"/>
+      <c r="E223" s="388"/>
+      <c r="F223" s="391"/>
     </row>
     <row r="224" spans="1:6">
-      <c r="A224" s="346"/>
-      <c r="B224" s="394"/>
+      <c r="A224" s="383"/>
+      <c r="B224" s="385"/>
       <c r="C224" s="67" t="s">
         <v>57</v>
       </c>
       <c r="D224" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E224" s="423"/>
-      <c r="F224" s="361"/>
+      <c r="E224" s="388"/>
+      <c r="F224" s="392"/>
     </row>
     <row r="225" spans="1:6">
-      <c r="A225" s="346"/>
-      <c r="B225" s="355" t="s">
+      <c r="A225" s="383"/>
+      <c r="B225" s="403" t="s">
         <v>38</v>
       </c>
       <c r="C225" s="73" t="s">
@@ -15030,62 +15024,62 @@
         <f>120000000/1000000</f>
         <v>120</v>
       </c>
-      <c r="E225" s="423"/>
-      <c r="F225" s="366" t="s">
+      <c r="E225" s="388"/>
+      <c r="F225" s="411" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="226" spans="1:6">
-      <c r="A226" s="346"/>
-      <c r="B226" s="355"/>
+      <c r="A226" s="383"/>
+      <c r="B226" s="403"/>
       <c r="C226" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D226" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="E226" s="423"/>
-      <c r="F226" s="360"/>
+      <c r="E226" s="388"/>
+      <c r="F226" s="391"/>
     </row>
     <row r="227" spans="1:6">
-      <c r="A227" s="346"/>
-      <c r="B227" s="355"/>
+      <c r="A227" s="383"/>
+      <c r="B227" s="403"/>
       <c r="C227" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D227" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="E227" s="423"/>
-      <c r="F227" s="360"/>
+      <c r="E227" s="388"/>
+      <c r="F227" s="391"/>
     </row>
     <row r="228" spans="1:6">
-      <c r="A228" s="346"/>
-      <c r="B228" s="355"/>
+      <c r="A228" s="383"/>
+      <c r="B228" s="403"/>
       <c r="C228" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D228" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="E228" s="423"/>
-      <c r="F228" s="360"/>
+      <c r="E228" s="388"/>
+      <c r="F228" s="391"/>
     </row>
     <row r="229" spans="1:6">
-      <c r="A229" s="346"/>
-      <c r="B229" s="355"/>
+      <c r="A229" s="383"/>
+      <c r="B229" s="403"/>
       <c r="C229" s="74" t="s">
         <v>57</v>
       </c>
       <c r="D229" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="E229" s="423"/>
-      <c r="F229" s="361"/>
+      <c r="E229" s="388"/>
+      <c r="F229" s="392"/>
     </row>
     <row r="230" spans="1:6">
-      <c r="A230" s="346"/>
-      <c r="B230" s="348" t="s">
+      <c r="A230" s="383"/>
+      <c r="B230" s="409" t="s">
         <v>40</v>
       </c>
       <c r="C230" s="73" t="s">
@@ -15095,108 +15089,187 @@
         <f>50000000/1000000</f>
         <v>50</v>
       </c>
-      <c r="E230" s="423"/>
-      <c r="F230" s="366">
+      <c r="E230" s="388"/>
+      <c r="F230" s="411">
         <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:6">
-      <c r="A231" s="346"/>
-      <c r="B231" s="348"/>
+      <c r="A231" s="383"/>
+      <c r="B231" s="409"/>
       <c r="C231" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D231" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E231" s="423"/>
-      <c r="F231" s="360"/>
+      <c r="E231" s="388"/>
+      <c r="F231" s="391"/>
     </row>
     <row r="232" spans="1:6">
-      <c r="A232" s="346"/>
-      <c r="B232" s="348"/>
+      <c r="A232" s="383"/>
+      <c r="B232" s="409"/>
       <c r="C232" s="75" t="s">
         <v>49</v>
       </c>
       <c r="D232" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E232" s="423"/>
-      <c r="F232" s="360"/>
+      <c r="E232" s="388"/>
+      <c r="F232" s="391"/>
     </row>
     <row r="233" spans="1:6">
-      <c r="A233" s="346"/>
-      <c r="B233" s="348"/>
-      <c r="C233" s="377" t="s">
+      <c r="A233" s="383"/>
+      <c r="B233" s="409"/>
+      <c r="C233" s="412" t="s">
         <v>51</v>
       </c>
       <c r="D233" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E233" s="423"/>
-      <c r="F233" s="360"/>
+      <c r="E233" s="388"/>
+      <c r="F233" s="391"/>
     </row>
     <row r="234" spans="1:6">
-      <c r="A234" s="346"/>
-      <c r="B234" s="348"/>
-      <c r="C234" s="378"/>
+      <c r="A234" s="383"/>
+      <c r="B234" s="409"/>
+      <c r="C234" s="413"/>
       <c r="D234" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="E234" s="423"/>
-      <c r="F234" s="360"/>
+      <c r="E234" s="388"/>
+      <c r="F234" s="391"/>
     </row>
     <row r="235" spans="1:6">
-      <c r="A235" s="346"/>
-      <c r="B235" s="348"/>
-      <c r="C235" s="378"/>
+      <c r="A235" s="383"/>
+      <c r="B235" s="409"/>
+      <c r="C235" s="413"/>
       <c r="D235" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="E235" s="423"/>
-      <c r="F235" s="360"/>
+      <c r="E235" s="388"/>
+      <c r="F235" s="391"/>
     </row>
     <row r="236" spans="1:6">
-      <c r="A236" s="346"/>
-      <c r="B236" s="348"/>
-      <c r="C236" s="379"/>
+      <c r="A236" s="383"/>
+      <c r="B236" s="409"/>
+      <c r="C236" s="414"/>
       <c r="D236" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="E236" s="423"/>
-      <c r="F236" s="360"/>
+      <c r="E236" s="388"/>
+      <c r="F236" s="391"/>
     </row>
     <row r="237" spans="1:6">
-      <c r="A237" s="346"/>
-      <c r="B237" s="417"/>
+      <c r="A237" s="383"/>
+      <c r="B237" s="410"/>
       <c r="C237" s="80" t="s">
         <v>57</v>
       </c>
       <c r="D237" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E237" s="424"/>
-      <c r="F237" s="361"/>
+      <c r="E237" s="389"/>
+      <c r="F237" s="392"/>
     </row>
   </sheetData>
   <mergeCells count="137">
-    <mergeCell ref="A199:A237"/>
-    <mergeCell ref="B199:B207"/>
-    <mergeCell ref="E199:E237"/>
-    <mergeCell ref="F199:F207"/>
-    <mergeCell ref="C202:C206"/>
-    <mergeCell ref="B208:B214"/>
-    <mergeCell ref="F208:F214"/>
-    <mergeCell ref="C211:C213"/>
-    <mergeCell ref="B215:B219"/>
-    <mergeCell ref="F215:F219"/>
-    <mergeCell ref="B220:B224"/>
-    <mergeCell ref="F220:F224"/>
-    <mergeCell ref="B225:B229"/>
-    <mergeCell ref="B230:B237"/>
-    <mergeCell ref="F230:F237"/>
-    <mergeCell ref="C233:C236"/>
-    <mergeCell ref="F225:F229"/>
+    <mergeCell ref="A43:A81"/>
+    <mergeCell ref="B74:B81"/>
+    <mergeCell ref="L50:N50"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="L52:N52"/>
+    <mergeCell ref="L40:N41"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="L46:N46"/>
+    <mergeCell ref="L47:N47"/>
+    <mergeCell ref="L48:N48"/>
+    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="B52:B58"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="B69:B73"/>
+    <mergeCell ref="F59:F63"/>
+    <mergeCell ref="F43:F51"/>
+    <mergeCell ref="F52:F58"/>
+    <mergeCell ref="F64:F68"/>
+    <mergeCell ref="F69:F73"/>
+    <mergeCell ref="B59:B63"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="E43:E81"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G34:R34"/>
+    <mergeCell ref="G35:R35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="G36:R36"/>
+    <mergeCell ref="G37:R37"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F74:F81"/>
+    <mergeCell ref="B43:B51"/>
+    <mergeCell ref="B137:B141"/>
+    <mergeCell ref="F137:F141"/>
+    <mergeCell ref="B121:B129"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="B1:I2"/>
+    <mergeCell ref="A29:F30"/>
+    <mergeCell ref="G31:R31"/>
+    <mergeCell ref="G33:R33"/>
+    <mergeCell ref="A31:F32"/>
+    <mergeCell ref="G32:R32"/>
+    <mergeCell ref="G29:R30"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="B152:B159"/>
+    <mergeCell ref="F152:F159"/>
+    <mergeCell ref="C155:C158"/>
+    <mergeCell ref="F191:F198"/>
+    <mergeCell ref="B160:B168"/>
+    <mergeCell ref="F169:F175"/>
+    <mergeCell ref="C172:C174"/>
+    <mergeCell ref="B176:B180"/>
+    <mergeCell ref="F176:F180"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="C163:C167"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="B186:B190"/>
+    <mergeCell ref="F186:F190"/>
+    <mergeCell ref="B191:B198"/>
+    <mergeCell ref="E121:E159"/>
+    <mergeCell ref="F121:F129"/>
+    <mergeCell ref="C124:C128"/>
+    <mergeCell ref="B142:B146"/>
+    <mergeCell ref="F142:F146"/>
+    <mergeCell ref="B147:B151"/>
+    <mergeCell ref="F147:F151"/>
+    <mergeCell ref="C133:C135"/>
     <mergeCell ref="A160:A198"/>
     <mergeCell ref="A121:A159"/>
     <mergeCell ref="F130:F136"/>
@@ -15221,102 +15294,23 @@
     <mergeCell ref="E160:E198"/>
     <mergeCell ref="F160:F168"/>
     <mergeCell ref="B169:B175"/>
-    <mergeCell ref="B152:B159"/>
-    <mergeCell ref="F152:F159"/>
-    <mergeCell ref="C155:C158"/>
-    <mergeCell ref="F191:F198"/>
-    <mergeCell ref="B160:B168"/>
-    <mergeCell ref="F169:F175"/>
-    <mergeCell ref="C172:C174"/>
-    <mergeCell ref="B176:B180"/>
-    <mergeCell ref="F176:F180"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="C163:C167"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="B186:B190"/>
-    <mergeCell ref="F186:F190"/>
-    <mergeCell ref="B191:B198"/>
-    <mergeCell ref="E121:E159"/>
-    <mergeCell ref="F121:F129"/>
-    <mergeCell ref="C124:C128"/>
-    <mergeCell ref="B142:B146"/>
-    <mergeCell ref="F142:F146"/>
-    <mergeCell ref="B147:B151"/>
-    <mergeCell ref="F147:F151"/>
-    <mergeCell ref="C133:C135"/>
-    <mergeCell ref="B137:B141"/>
-    <mergeCell ref="F137:F141"/>
-    <mergeCell ref="B121:B129"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="B1:I2"/>
-    <mergeCell ref="A29:F30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="G33:R33"/>
-    <mergeCell ref="A31:F32"/>
-    <mergeCell ref="G32:R32"/>
-    <mergeCell ref="G29:R30"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="E43:E81"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="G34:R34"/>
-    <mergeCell ref="G35:R35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="G36:R36"/>
-    <mergeCell ref="G37:R37"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F74:F81"/>
-    <mergeCell ref="B43:B51"/>
-    <mergeCell ref="A43:A81"/>
-    <mergeCell ref="B74:B81"/>
-    <mergeCell ref="L50:N50"/>
-    <mergeCell ref="L51:N51"/>
-    <mergeCell ref="L52:N52"/>
-    <mergeCell ref="L40:N41"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="L43:N43"/>
-    <mergeCell ref="L44:N44"/>
-    <mergeCell ref="L45:N45"/>
-    <mergeCell ref="L46:N46"/>
-    <mergeCell ref="L47:N47"/>
-    <mergeCell ref="L48:N48"/>
-    <mergeCell ref="L49:N49"/>
-    <mergeCell ref="B52:B58"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="B69:B73"/>
-    <mergeCell ref="F59:F63"/>
-    <mergeCell ref="F43:F51"/>
-    <mergeCell ref="F52:F58"/>
-    <mergeCell ref="F64:F68"/>
-    <mergeCell ref="F69:F73"/>
-    <mergeCell ref="B59:B63"/>
-    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="A199:A237"/>
+    <mergeCell ref="B199:B207"/>
+    <mergeCell ref="E199:E237"/>
+    <mergeCell ref="F199:F207"/>
+    <mergeCell ref="C202:C206"/>
+    <mergeCell ref="B208:B214"/>
+    <mergeCell ref="F208:F214"/>
+    <mergeCell ref="C211:C213"/>
+    <mergeCell ref="B215:B219"/>
+    <mergeCell ref="F215:F219"/>
+    <mergeCell ref="B220:B224"/>
+    <mergeCell ref="F220:F224"/>
+    <mergeCell ref="B225:B229"/>
+    <mergeCell ref="B230:B237"/>
+    <mergeCell ref="F230:F237"/>
+    <mergeCell ref="C233:C236"/>
+    <mergeCell ref="F225:F229"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15337,14 +15331,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="51.75" customHeight="1">
-      <c r="B1" s="437" t="s">
+      <c r="B1" s="475" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="438"/>
-      <c r="D1" s="438"/>
-      <c r="E1" s="438"/>
-      <c r="F1" s="438"/>
-      <c r="G1" s="439"/>
+      <c r="C1" s="476"/>
+      <c r="D1" s="476"/>
+      <c r="E1" s="476"/>
+      <c r="F1" s="476"/>
+      <c r="G1" s="477"/>
     </row>
     <row r="2" spans="2:7">
       <c r="B2" s="290"/>
@@ -15606,12 +15600,12 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="21.75" customHeight="1">
-      <c r="B16" s="440" t="s">
+      <c r="B16" s="478" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="440"/>
-      <c r="D16" s="440"/>
-      <c r="E16" s="440"/>
+      <c r="C16" s="478"/>
+      <c r="D16" s="478"/>
+      <c r="E16" s="478"/>
     </row>
     <row r="17" spans="2:5" ht="21.75" customHeight="1">
       <c r="B17" s="340" t="s">
@@ -15622,12 +15616,12 @@
       <c r="E17" s="294"/>
     </row>
     <row r="18" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B18" s="441" t="s">
+      <c r="B18" s="479" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="442"/>
-      <c r="D18" s="442"/>
-      <c r="E18" s="443"/>
+      <c r="C18" s="480"/>
+      <c r="D18" s="480"/>
+      <c r="E18" s="481"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -15649,7 +15643,7 @@
     <col min="3" max="3" width="23.28515625" style="4" customWidth="1"/>
     <col min="4" max="4" width="29.5703125" style="4" customWidth="1"/>
     <col min="5" max="5" width="27.42578125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" style="567" customWidth="1"/>
+    <col min="6" max="6" width="42.28515625" style="363" customWidth="1"/>
     <col min="7" max="7" width="25.5703125" style="4" customWidth="1"/>
     <col min="8" max="8" width="23.140625" style="4" customWidth="1"/>
     <col min="9" max="9" width="23.28515625" style="2" customWidth="1"/>
@@ -15657,21 +15651,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="35.25" customHeight="1">
-      <c r="B2" s="444" t="s">
+      <c r="B2" s="341" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="444"/>
-      <c r="D2" s="444"/>
-      <c r="E2" s="444"/>
-      <c r="F2" s="566"/>
+      <c r="C2" s="341"/>
+      <c r="D2" s="341"/>
+      <c r="E2" s="341"/>
+      <c r="F2" s="362"/>
     </row>
     <row r="3" spans="2:6" ht="51" customHeight="1">
-      <c r="B3" s="456" t="s">
+      <c r="B3" s="353" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="456"/>
-      <c r="D3" s="456"/>
-      <c r="E3" s="456"/>
+      <c r="C3" s="353"/>
+      <c r="D3" s="353"/>
+      <c r="E3" s="353"/>
     </row>
     <row r="4" spans="2:6" ht="30" customHeight="1">
       <c r="B4" s="155" t="s">
@@ -15714,7 +15708,7 @@
       <c r="E6" s="144">
         <v>3</v>
       </c>
-      <c r="F6" s="568"/>
+      <c r="F6" s="364"/>
     </row>
     <row r="7" spans="2:6" ht="21.75" customHeight="1">
       <c r="B7" s="141" t="s">
@@ -15729,7 +15723,7 @@
       <c r="E7" s="142">
         <v>7</v>
       </c>
-      <c r="F7" s="569"/>
+      <c r="F7" s="365"/>
     </row>
     <row r="8" spans="2:6" ht="23.25" customHeight="1">
       <c r="B8" s="141" t="s">
@@ -15744,12 +15738,12 @@
       <c r="E8" s="142">
         <v>10</v>
       </c>
-      <c r="F8" s="569"/>
+      <c r="F8" s="365"/>
     </row>
     <row r="9" spans="2:6" ht="23.25" customHeight="1">
       <c r="D9" s="139"/>
       <c r="E9" s="24"/>
-      <c r="F9" s="570"/>
+      <c r="F9" s="366"/>
     </row>
     <row r="10" spans="2:6" ht="29.25" customHeight="1">
       <c r="B10" s="155" t="s">
@@ -15764,7 +15758,7 @@
       <c r="E10" s="155" t="s">
         <v>117</v>
       </c>
-      <c r="F10" s="571" t="s">
+      <c r="F10" s="367" t="s">
         <v>118</v>
       </c>
     </row>
@@ -15781,7 +15775,7 @@
       <c r="E11" s="141">
         <v>2000</v>
       </c>
-      <c r="F11" s="572">
+      <c r="F11" s="368">
         <f>(D11/C11)*100</f>
         <v>80</v>
       </c>
@@ -15799,7 +15793,7 @@
       <c r="E12" s="141">
         <v>1800</v>
       </c>
-      <c r="F12" s="572">
+      <c r="F12" s="368">
         <f>(D12/C12)*100</f>
         <v>80</v>
       </c>
@@ -15817,7 +15811,7 @@
       <c r="E13" s="141">
         <v>2200</v>
       </c>
-      <c r="F13" s="572">
+      <c r="F13" s="368">
         <f>(D13/C13)*100</f>
         <v>80</v>
       </c>
@@ -15835,7 +15829,7 @@
       <c r="E14" s="141">
         <v>1900</v>
       </c>
-      <c r="F14" s="572">
+      <c r="F14" s="368">
         <f>(D14/C14)*100</f>
         <v>80</v>
       </c>
@@ -15853,7 +15847,7 @@
       <c r="E15" s="249">
         <v>1600</v>
       </c>
-      <c r="F15" s="573">
+      <c r="F15" s="369">
         <f>(D15/C15)*100</f>
         <v>80</v>
       </c>
@@ -15871,7 +15865,7 @@
       <c r="E16" s="142">
         <v>15000</v>
       </c>
-      <c r="F16" s="572">
+      <c r="F16" s="368">
         <f>D16/C16*100</f>
         <v>80</v>
       </c>
@@ -15889,7 +15883,7 @@
       <c r="E17" s="142">
         <v>25000</v>
       </c>
-      <c r="F17" s="572">
+      <c r="F17" s="368">
         <f>D17/C17*100</f>
         <v>80</v>
       </c>
@@ -15907,7 +15901,7 @@
       <c r="E18" s="142">
         <v>20000</v>
       </c>
-      <c r="F18" s="572">
+      <c r="F18" s="368">
         <f>D18/C18*100</f>
         <v>85</v>
       </c>
@@ -15925,7 +15919,7 @@
       <c r="E19" s="249">
         <v>18000</v>
       </c>
-      <c r="F19" s="573">
+      <c r="F19" s="369">
         <f>D19/C19*100</f>
         <v>86</v>
       </c>
@@ -15943,7 +15937,7 @@
       <c r="E20" s="142">
         <v>1500</v>
       </c>
-      <c r="F20" s="572">
+      <c r="F20" s="368">
         <f>D20/C20*100</f>
         <v>85</v>
       </c>
@@ -15961,7 +15955,7 @@
       <c r="E21" s="142">
         <v>3000</v>
       </c>
-      <c r="F21" s="572">
+      <c r="F21" s="368">
         <f>D21/C21*100</f>
         <v>85</v>
       </c>
@@ -15969,97 +15963,97 @@
     <row r="22" spans="2:6" ht="23.25" customHeight="1">
       <c r="D22" s="139"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="570"/>
+      <c r="F22" s="366"/>
     </row>
     <row r="23" spans="2:6" ht="44.25" customHeight="1">
-      <c r="B23" s="456" t="s">
+      <c r="B23" s="353" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="456"/>
-      <c r="D23" s="456"/>
+      <c r="C23" s="353"/>
+      <c r="D23" s="353"/>
       <c r="E23" s="24"/>
-      <c r="F23" s="570"/>
+      <c r="F23" s="366"/>
     </row>
     <row r="24" spans="2:6" ht="30" customHeight="1">
       <c r="B24" s="155" t="s">
         <v>120</v>
       </c>
-      <c r="C24" s="459" t="s">
+      <c r="C24" s="356" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="460"/>
+      <c r="D24" s="357"/>
       <c r="E24" s="24"/>
-      <c r="F24" s="570"/>
+      <c r="F24" s="366"/>
     </row>
     <row r="25" spans="2:6" ht="23.25" customHeight="1">
       <c r="B25" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="461" t="s">
+      <c r="C25" s="358" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="462"/>
+      <c r="D25" s="359"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="570"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6" ht="23.25" customHeight="1">
       <c r="B26" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="461" t="s">
+      <c r="C26" s="358" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="462"/>
+      <c r="D26" s="359"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="570"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6" ht="23.25" customHeight="1">
       <c r="B27" s="141" t="s">
         <v>126</v>
       </c>
-      <c r="C27" s="461" t="s">
+      <c r="C27" s="358" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="462"/>
+      <c r="D27" s="359"/>
       <c r="E27" s="24"/>
-      <c r="F27" s="570"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6" ht="23.25" customHeight="1">
       <c r="B28" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="461" t="s">
+      <c r="C28" s="358" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="462"/>
+      <c r="D28" s="359"/>
       <c r="E28" s="24"/>
-      <c r="F28" s="570"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="29" spans="2:6" ht="23.25" customHeight="1">
       <c r="B29" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="461" t="s">
+      <c r="C29" s="358" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="462"/>
+      <c r="D29" s="359"/>
       <c r="E29" s="24"/>
-      <c r="F29" s="570"/>
+      <c r="F29" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="23.25" customHeight="1">
       <c r="C30"/>
       <c r="D30" s="139"/>
       <c r="E30" s="24"/>
-      <c r="F30" s="570"/>
+      <c r="F30" s="366"/>
     </row>
     <row r="31" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B31" s="454" t="s">
+      <c r="B31" s="351" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="455"/>
-      <c r="D31" s="455"/>
-      <c r="E31" s="455"/>
-      <c r="F31" s="455"/>
+      <c r="C31" s="352"/>
+      <c r="D31" s="352"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6" ht="32.25" customHeight="1">
       <c r="B32" s="155" t="s">
@@ -16074,7 +16068,7 @@
       <c r="E32" s="155" t="s">
         <v>136</v>
       </c>
-      <c r="F32" s="571" t="s">
+      <c r="F32" s="367" t="s">
         <v>137</v>
       </c>
     </row>
@@ -16091,7 +16085,7 @@
       <c r="E33" s="209">
         <v>8100000</v>
       </c>
-      <c r="F33" s="574">
+      <c r="F33" s="370">
         <v>43200000</v>
       </c>
     </row>
@@ -16108,7 +16102,7 @@
       <c r="E34" s="209">
         <v>5500000</v>
       </c>
-      <c r="F34" s="574">
+      <c r="F34" s="370">
         <v>9450000</v>
       </c>
     </row>
@@ -16125,7 +16119,7 @@
       <c r="E35" s="209">
         <v>2000000</v>
       </c>
-      <c r="F35" s="574">
+      <c r="F35" s="370">
         <v>4000000</v>
       </c>
     </row>
@@ -16142,7 +16136,7 @@
       <c r="E36" s="209">
         <v>1800000</v>
       </c>
-      <c r="F36" s="574">
+      <c r="F36" s="370">
         <v>3500000</v>
       </c>
     </row>
@@ -16162,7 +16156,7 @@
         <f>(E33+E34+E35+E36)</f>
         <v>17400000</v>
       </c>
-      <c r="F37" s="574">
+      <c r="F37" s="370">
         <f>(F33+F34+F35+F36)</f>
         <v>60150000</v>
       </c>
@@ -16171,16 +16165,16 @@
       <c r="C38"/>
       <c r="D38" s="139"/>
       <c r="E38" s="24"/>
-      <c r="F38" s="570"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B39" s="454" t="s">
+      <c r="B39" s="351" t="s">
         <v>143</v>
       </c>
-      <c r="C39" s="455"/>
-      <c r="D39" s="455"/>
+      <c r="C39" s="352"/>
+      <c r="D39" s="352"/>
       <c r="E39" s="24"/>
-      <c r="F39" s="570"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6" ht="31.5" customHeight="1">
       <c r="B40" s="155" t="s">
@@ -16193,7 +16187,7 @@
         <v>145</v>
       </c>
       <c r="E40" s="24"/>
-      <c r="F40" s="570"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="41" spans="2:6" ht="23.25" customHeight="1">
       <c r="B41" s="141" t="s">
@@ -16206,7 +16200,7 @@
         <v>313887</v>
       </c>
       <c r="E41" s="24"/>
-      <c r="F41" s="570"/>
+      <c r="F41" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="23.25" customHeight="1">
       <c r="B42" s="141" t="s">
@@ -16219,7 +16213,7 @@
         <v>9416610</v>
       </c>
       <c r="E42" s="24"/>
-      <c r="F42" s="570"/>
+      <c r="F42" s="366"/>
     </row>
     <row r="43" spans="2:6" ht="23.25" customHeight="1">
       <c r="B43" s="141" t="s">
@@ -16232,7 +16226,7 @@
         <v>101250000</v>
       </c>
       <c r="E43" s="24"/>
-      <c r="F43" s="570"/>
+      <c r="F43" s="366"/>
     </row>
     <row r="44" spans="2:6" ht="23.25" customHeight="1">
       <c r="B44" s="141" t="s">
@@ -16245,22 +16239,22 @@
         <v>216000000</v>
       </c>
       <c r="E44" s="24"/>
-      <c r="F44" s="570"/>
+      <c r="F44" s="366"/>
     </row>
     <row r="45" spans="2:6" ht="23.25" customHeight="1">
       <c r="C45" s="7"/>
       <c r="D45" s="139"/>
       <c r="E45" s="24"/>
-      <c r="F45" s="570"/>
+      <c r="F45" s="366"/>
     </row>
     <row r="46" spans="2:6" ht="45" customHeight="1">
-      <c r="B46" s="457" t="s">
+      <c r="B46" s="354" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="458"/>
-      <c r="D46" s="458"/>
-      <c r="E46" s="458"/>
-      <c r="F46" s="458"/>
+      <c r="C46" s="355"/>
+      <c r="D46" s="355"/>
+      <c r="E46" s="355"/>
+      <c r="F46" s="355"/>
     </row>
     <row r="47" spans="2:6" ht="31.5" customHeight="1">
       <c r="B47" s="156"/>
@@ -16273,7 +16267,7 @@
       <c r="E47" s="157" t="s">
         <v>149</v>
       </c>
-      <c r="F47" s="575" t="s">
+      <c r="F47" s="371" t="s">
         <v>150</v>
       </c>
     </row>
@@ -16290,7 +16284,7 @@
       <c r="E48" s="209">
         <v>125554</v>
       </c>
-      <c r="F48" s="574">
+      <c r="F48" s="370">
         <f>(D48-E48)</f>
         <v>502220</v>
       </c>
@@ -16308,7 +16302,7 @@
       <c r="E49" s="209">
         <v>251109</v>
       </c>
-      <c r="F49" s="574">
+      <c r="F49" s="370">
         <f>(D49-E49)</f>
         <v>690552</v>
       </c>
@@ -16326,7 +16320,7 @@
       <c r="E50" s="209">
         <v>439441</v>
       </c>
-      <c r="F50" s="574">
+      <c r="F50" s="370">
         <f>(D50-E50)</f>
         <v>816107</v>
       </c>
@@ -16335,47 +16329,47 @@
       <c r="C51"/>
       <c r="D51" s="139"/>
       <c r="E51" s="24"/>
-      <c r="F51" s="570"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:9" ht="23.25" customHeight="1">
       <c r="C52"/>
       <c r="D52" s="139"/>
       <c r="E52" s="24"/>
-      <c r="F52" s="570"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="53" spans="2:9" ht="23.25" customHeight="1">
       <c r="C53"/>
       <c r="D53" s="139"/>
       <c r="E53" s="24"/>
-      <c r="F53" s="570"/>
+      <c r="F53" s="366"/>
     </row>
     <row r="54" spans="2:9" ht="23.25" customHeight="1">
       <c r="C54"/>
       <c r="D54" s="139"/>
       <c r="E54" s="24"/>
-      <c r="F54" s="570"/>
+      <c r="F54" s="366"/>
     </row>
     <row r="55" spans="2:9" ht="23.25" customHeight="1">
       <c r="C55"/>
       <c r="D55" s="139"/>
       <c r="E55" s="24"/>
-      <c r="F55" s="570"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:9" ht="23.25" customHeight="1">
       <c r="C56"/>
       <c r="D56" s="139"/>
       <c r="E56" s="24"/>
-      <c r="F56" s="570"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:9" ht="23.25" customHeight="1">
       <c r="C57"/>
       <c r="D57" s="139"/>
       <c r="E57" s="24"/>
-      <c r="F57" s="570"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:9" ht="23.25" customHeight="1">
       <c r="E58" s="64"/>
-      <c r="F58" s="576" t="s">
+      <c r="F58" s="372" t="s">
         <v>154</v>
       </c>
       <c r="G58" s="65"/>
@@ -16384,56 +16378,56 @@
     </row>
     <row r="59" spans="2:9" ht="23.25" customHeight="1">
       <c r="E59" s="24"/>
-      <c r="F59" s="577"/>
-      <c r="G59" s="341"/>
+      <c r="F59" s="373"/>
+      <c r="G59" s="346"/>
     </row>
     <row r="60" spans="2:9" ht="24" customHeight="1">
       <c r="E60" s="211"/>
-      <c r="F60" s="578" t="s">
+      <c r="F60" s="374" t="s">
         <v>155</v>
       </c>
-      <c r="G60" s="445" t="s">
+      <c r="G60" s="342" t="s">
         <v>156</v>
       </c>
-      <c r="H60" s="446"/>
-      <c r="I60" s="447"/>
+      <c r="H60" s="343"/>
+      <c r="I60" s="344"/>
     </row>
     <row r="61" spans="2:9" ht="29.25" customHeight="1">
       <c r="E61" s="59"/>
-      <c r="F61" s="579" t="s">
+      <c r="F61" s="375" t="s">
         <v>157</v>
       </c>
       <c r="G61" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="H61" s="341"/>
+      <c r="H61" s="346"/>
       <c r="I61" s="214"/>
     </row>
     <row r="62" spans="2:9" ht="30" customHeight="1">
       <c r="E62" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="F62" s="579" t="s">
+      <c r="F62" s="375" t="s">
         <v>160</v>
       </c>
       <c r="G62" s="69" t="s">
         <v>161</v>
       </c>
-      <c r="H62" s="341"/>
+      <c r="H62" s="346"/>
       <c r="I62" s="214"/>
     </row>
     <row r="63" spans="2:9" ht="31.5" customHeight="1">
       <c r="E63" s="61"/>
-      <c r="F63" s="580" t="s">
+      <c r="F63" s="376" t="s">
         <v>162</v>
       </c>
-      <c r="G63" s="448"/>
-      <c r="H63" s="449"/>
-      <c r="I63" s="450"/>
+      <c r="G63" s="345"/>
+      <c r="H63" s="346"/>
+      <c r="I63" s="347"/>
     </row>
     <row r="64" spans="2:9" ht="31.5" customHeight="1">
       <c r="E64" s="50"/>
-      <c r="F64" s="581" t="s">
+      <c r="F64" s="377" t="s">
         <v>163</v>
       </c>
       <c r="G64" s="68" t="s">
@@ -16446,18 +16440,18 @@
       <c r="E65" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="F65" s="579" t="s">
+      <c r="F65" s="375" t="s">
         <v>166</v>
       </c>
       <c r="G65" s="69" t="s">
         <v>167</v>
       </c>
-      <c r="H65" s="341"/>
+      <c r="H65" s="346"/>
       <c r="I65" s="214"/>
     </row>
     <row r="66" spans="5:9" ht="29.25" customHeight="1">
       <c r="E66" s="52"/>
-      <c r="F66" s="579" t="s">
+      <c r="F66" s="375" t="s">
         <v>168</v>
       </c>
       <c r="G66" s="70" t="s">
@@ -16468,42 +16462,42 @@
     </row>
     <row r="67" spans="5:9" ht="28.5" customHeight="1">
       <c r="E67" s="53"/>
-      <c r="F67" s="582" t="s">
+      <c r="F67" s="378" t="s">
         <v>170</v>
       </c>
-      <c r="G67" s="342" t="s">
+      <c r="G67" s="350" t="s">
         <v>171</v>
       </c>
-      <c r="H67" s="341"/>
+      <c r="H67" s="346"/>
       <c r="I67" s="214"/>
     </row>
     <row r="68" spans="5:9" ht="29.25" customHeight="1">
       <c r="E68" s="54" t="s">
         <v>172</v>
       </c>
-      <c r="F68" s="583" t="s">
+      <c r="F68" s="379" t="s">
         <v>173</v>
       </c>
-      <c r="G68" s="342" t="s">
+      <c r="G68" s="350" t="s">
         <v>174</v>
       </c>
-      <c r="H68" s="341"/>
+      <c r="H68" s="346"/>
       <c r="I68" s="214"/>
     </row>
     <row r="69" spans="5:9" ht="28.5" customHeight="1">
       <c r="E69" s="55"/>
-      <c r="F69" s="583" t="s">
+      <c r="F69" s="379" t="s">
         <v>175</v>
       </c>
-      <c r="G69" s="342" t="s">
+      <c r="G69" s="350" t="s">
         <v>176</v>
       </c>
-      <c r="H69" s="341"/>
+      <c r="H69" s="346"/>
       <c r="I69" s="214"/>
     </row>
     <row r="70" spans="5:9" ht="29.25" customHeight="1">
       <c r="E70" s="56"/>
-      <c r="F70" s="584" t="s">
+      <c r="F70" s="380" t="s">
         <v>177</v>
       </c>
       <c r="G70" s="219" t="s">
@@ -16516,18 +16510,18 @@
       <c r="E71" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="F71" s="585" t="s">
+      <c r="F71" s="381" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="451" t="s">
+      <c r="G71" s="348" t="s">
         <v>181</v>
       </c>
-      <c r="H71" s="452"/>
-      <c r="I71" s="453"/>
+      <c r="H71" s="349"/>
+      <c r="I71" s="350"/>
     </row>
     <row r="72" spans="5:9" ht="29.25" customHeight="1">
       <c r="E72" s="58"/>
-      <c r="F72" s="586" t="s">
+      <c r="F72" s="382" t="s">
         <v>182</v>
       </c>
       <c r="G72" s="215" t="s">
@@ -16541,23 +16535,6 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E4">
     <sortCondition sortBy="cellColor" ref="B4" dxfId="142"/>
   </sortState>
-  <mergeCells count="15">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="G60:I60"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B23:D23"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16582,49 +16559,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15">
-      <c r="A2" s="464" t="s">
+      <c r="A2" s="499" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="465"/>
-      <c r="C2" s="465"/>
-      <c r="D2" s="465"/>
-      <c r="E2" s="465"/>
-      <c r="F2" s="465"/>
-      <c r="G2" s="465"/>
-      <c r="H2" s="465"/>
-      <c r="I2" s="465"/>
-      <c r="J2" s="465"/>
-      <c r="K2" s="465"/>
-      <c r="L2" s="465"/>
-      <c r="M2" s="465"/>
-      <c r="N2" s="465"/>
-      <c r="O2" s="465"/>
+      <c r="B2" s="500"/>
+      <c r="C2" s="500"/>
+      <c r="D2" s="500"/>
+      <c r="E2" s="500"/>
+      <c r="F2" s="500"/>
+      <c r="G2" s="500"/>
+      <c r="H2" s="500"/>
+      <c r="I2" s="500"/>
+      <c r="J2" s="500"/>
+      <c r="K2" s="500"/>
+      <c r="L2" s="500"/>
+      <c r="M2" s="500"/>
+      <c r="N2" s="500"/>
+      <c r="O2" s="500"/>
     </row>
     <row r="3" spans="1:15" ht="84" customHeight="1">
-      <c r="A3" s="465"/>
-      <c r="B3" s="465"/>
-      <c r="C3" s="465"/>
-      <c r="D3" s="465"/>
-      <c r="E3" s="465"/>
-      <c r="F3" s="465"/>
-      <c r="G3" s="465"/>
-      <c r="H3" s="465"/>
-      <c r="I3" s="465"/>
-      <c r="J3" s="465"/>
-      <c r="K3" s="465"/>
-      <c r="L3" s="465"/>
-      <c r="M3" s="465"/>
-      <c r="N3" s="465"/>
-      <c r="O3" s="465"/>
+      <c r="A3" s="500"/>
+      <c r="B3" s="500"/>
+      <c r="C3" s="500"/>
+      <c r="D3" s="500"/>
+      <c r="E3" s="500"/>
+      <c r="F3" s="500"/>
+      <c r="G3" s="500"/>
+      <c r="H3" s="500"/>
+      <c r="I3" s="500"/>
+      <c r="J3" s="500"/>
+      <c r="K3" s="500"/>
+      <c r="L3" s="500"/>
+      <c r="M3" s="500"/>
+      <c r="N3" s="500"/>
+      <c r="O3" s="500"/>
     </row>
     <row r="5" spans="1:15" ht="45">
-      <c r="B5" s="475" t="s">
+      <c r="B5" s="486" t="s">
         <v>185</v>
       </c>
-      <c r="C5" s="475"/>
-      <c r="D5" s="475"/>
-      <c r="E5" s="475"/>
-      <c r="F5" s="475"/>
+      <c r="C5" s="486"/>
+      <c r="D5" s="486"/>
+      <c r="E5" s="486"/>
+      <c r="F5" s="486"/>
       <c r="G5" s="158"/>
       <c r="H5" s="158"/>
       <c r="I5" s="158"/>
@@ -16656,12 +16633,12 @@
       <c r="I6" s="163"/>
       <c r="J6" s="163"/>
       <c r="K6" s="158"/>
-      <c r="L6" s="479" t="s">
+      <c r="L6" s="490" t="s">
         <v>190</v>
       </c>
-      <c r="M6" s="479"/>
-      <c r="N6" s="479"/>
-      <c r="O6" s="479"/>
+      <c r="M6" s="490"/>
+      <c r="N6" s="490"/>
+      <c r="O6" s="490"/>
     </row>
     <row r="7" spans="1:15" ht="23.25">
       <c r="B7" s="187" t="s">
@@ -16684,7 +16661,7 @@
       <c r="I7" s="166"/>
       <c r="J7" s="166"/>
       <c r="K7" s="167"/>
-      <c r="L7" s="480" t="s">
+      <c r="L7" s="491" t="s">
         <v>195</v>
       </c>
       <c r="M7" s="168" t="s">
@@ -16693,7 +16670,7 @@
       <c r="N7" s="169" t="s">
         <v>197</v>
       </c>
-      <c r="O7" s="480" t="s">
+      <c r="O7" s="491" t="s">
         <v>198</v>
       </c>
     </row>
@@ -16718,12 +16695,12 @@
       <c r="I8" s="171"/>
       <c r="J8" s="171"/>
       <c r="K8" s="167"/>
-      <c r="L8" s="480"/>
-      <c r="M8" s="481" t="s">
+      <c r="L8" s="491"/>
+      <c r="M8" s="492" t="s">
         <v>203</v>
       </c>
-      <c r="N8" s="481"/>
-      <c r="O8" s="480"/>
+      <c r="N8" s="492"/>
+      <c r="O8" s="491"/>
     </row>
     <row r="9" spans="1:15" ht="23.25">
       <c r="B9" s="189" t="s">
@@ -16746,14 +16723,14 @@
       <c r="I9" s="174"/>
       <c r="J9" s="174"/>
       <c r="K9" s="167"/>
-      <c r="L9" s="480"/>
+      <c r="L9" s="491"/>
       <c r="M9" s="43" t="s">
         <v>206</v>
       </c>
       <c r="N9" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="O9" s="480"/>
+      <c r="O9" s="491"/>
     </row>
     <row r="10" spans="1:15" ht="23.25">
       <c r="B10" s="158"/>
@@ -16766,36 +16743,36 @@
       <c r="I10" s="174"/>
       <c r="J10" s="174"/>
       <c r="K10" s="167"/>
-      <c r="L10" s="480"/>
+      <c r="L10" s="491"/>
       <c r="M10" s="46" t="s">
         <v>208</v>
       </c>
       <c r="N10" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="O10" s="480"/>
+      <c r="O10" s="491"/>
     </row>
     <row r="11" spans="1:15" ht="45.75">
-      <c r="B11" s="484" t="s">
+      <c r="B11" s="495" t="s">
         <v>210</v>
       </c>
-      <c r="C11" s="485"/>
-      <c r="D11" s="485"/>
-      <c r="E11" s="485"/>
-      <c r="F11" s="485"/>
-      <c r="G11" s="485"/>
-      <c r="H11" s="486"/>
+      <c r="C11" s="496"/>
+      <c r="D11" s="496"/>
+      <c r="E11" s="496"/>
+      <c r="F11" s="496"/>
+      <c r="G11" s="496"/>
+      <c r="H11" s="497"/>
       <c r="I11" s="174"/>
       <c r="J11" s="174"/>
       <c r="K11" s="167"/>
-      <c r="L11" s="480"/>
+      <c r="L11" s="491"/>
       <c r="M11" s="46" t="s">
         <v>211</v>
       </c>
       <c r="N11" s="176" t="s">
         <v>212</v>
       </c>
-      <c r="O11" s="480"/>
+      <c r="O11" s="491"/>
     </row>
     <row r="12" spans="1:15" ht="23.25">
       <c r="B12" s="177" t="s">
@@ -16822,12 +16799,12 @@
       <c r="I12" s="158"/>
       <c r="J12" s="158"/>
       <c r="K12" s="158"/>
-      <c r="L12" s="480"/>
-      <c r="M12" s="482" t="s">
+      <c r="L12" s="491"/>
+      <c r="M12" s="493" t="s">
         <v>218</v>
       </c>
-      <c r="N12" s="482"/>
-      <c r="O12" s="480"/>
+      <c r="N12" s="493"/>
+      <c r="O12" s="491"/>
     </row>
     <row r="13" spans="1:15" ht="23.25">
       <c r="B13" s="178" t="s">
@@ -16842,7 +16819,7 @@
       <c r="E13" s="178">
         <v>800</v>
       </c>
-      <c r="F13" s="470" t="s">
+      <c r="F13" s="503" t="s">
         <v>221</v>
       </c>
       <c r="G13" s="192">
@@ -16856,14 +16833,14 @@
       <c r="I13" s="158"/>
       <c r="J13" s="158"/>
       <c r="K13" s="158"/>
-      <c r="L13" s="480"/>
+      <c r="L13" s="491"/>
       <c r="M13" s="43" t="s">
         <v>222</v>
       </c>
       <c r="N13" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="O13" s="480"/>
+      <c r="O13" s="491"/>
     </row>
     <row r="14" spans="1:15" ht="23.25">
       <c r="B14" s="178" t="s">
@@ -16878,7 +16855,7 @@
       <c r="E14" s="192">
         <v>1200</v>
       </c>
-      <c r="F14" s="471"/>
+      <c r="F14" s="504"/>
       <c r="G14" s="192">
         <f>600*650</f>
         <v>390000</v>
@@ -16890,14 +16867,14 @@
       <c r="I14" s="158"/>
       <c r="J14" s="158"/>
       <c r="K14" s="158"/>
-      <c r="L14" s="480"/>
+      <c r="L14" s="491"/>
       <c r="M14" s="46" t="s">
         <v>225</v>
       </c>
       <c r="N14" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="O14" s="480"/>
+      <c r="O14" s="491"/>
     </row>
     <row r="15" spans="1:15" ht="23.25">
       <c r="B15" s="178" t="s">
@@ -16912,7 +16889,7 @@
       <c r="E15" s="178">
         <v>800</v>
       </c>
-      <c r="F15" s="472"/>
+      <c r="F15" s="505"/>
       <c r="G15" s="192">
         <f>320*650</f>
         <v>208000</v>
@@ -16924,12 +16901,12 @@
       <c r="I15" s="158"/>
       <c r="J15" s="158"/>
       <c r="K15" s="158"/>
-      <c r="L15" s="480"/>
-      <c r="M15" s="481" t="s">
+      <c r="L15" s="491"/>
+      <c r="M15" s="492" t="s">
         <v>227</v>
       </c>
-      <c r="N15" s="481"/>
-      <c r="O15" s="480"/>
+      <c r="N15" s="492"/>
+      <c r="O15" s="491"/>
     </row>
     <row r="16" spans="1:15" ht="23.25">
       <c r="B16" s="178" t="s">
@@ -16956,14 +16933,14 @@
       <c r="I16" s="158"/>
       <c r="J16" s="158"/>
       <c r="K16" s="158"/>
-      <c r="L16" s="480"/>
+      <c r="L16" s="491"/>
       <c r="M16" s="43" t="s">
         <v>232</v>
       </c>
       <c r="N16" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="O16" s="480"/>
+      <c r="O16" s="491"/>
     </row>
     <row r="17" spans="2:15" ht="23.25">
       <c r="B17" s="178" t="s">
@@ -16988,14 +16965,14 @@
       <c r="I17" s="158"/>
       <c r="J17" s="158"/>
       <c r="K17" s="158"/>
-      <c r="L17" s="480"/>
+      <c r="L17" s="491"/>
       <c r="M17" s="48" t="s">
         <v>235</v>
       </c>
       <c r="N17" s="85" t="s">
         <v>236</v>
       </c>
-      <c r="O17" s="480"/>
+      <c r="O17" s="491"/>
     </row>
     <row r="18" spans="2:15" ht="23.25">
       <c r="B18" s="179"/>
@@ -17008,14 +16985,14 @@
       <c r="I18" s="158"/>
       <c r="J18" s="158"/>
       <c r="K18" s="158"/>
-      <c r="L18" s="480"/>
+      <c r="L18" s="491"/>
       <c r="M18" s="182" t="s">
         <v>165</v>
       </c>
       <c r="N18" s="183" t="s">
         <v>179</v>
       </c>
-      <c r="O18" s="480"/>
+      <c r="O18" s="491"/>
     </row>
     <row r="19" spans="2:15" ht="23.25">
       <c r="B19" s="158"/>
@@ -17028,12 +17005,12 @@
       <c r="I19" s="158"/>
       <c r="J19" s="158"/>
       <c r="K19" s="158"/>
-      <c r="L19" s="480"/>
-      <c r="M19" s="481" t="s">
+      <c r="L19" s="491"/>
+      <c r="M19" s="492" t="s">
         <v>203</v>
       </c>
-      <c r="N19" s="483"/>
-      <c r="O19" s="480"/>
+      <c r="N19" s="494"/>
+      <c r="O19" s="491"/>
     </row>
     <row r="20" spans="2:15" ht="23.25">
       <c r="B20" s="158"/>
@@ -17046,21 +17023,21 @@
       <c r="I20" s="158"/>
       <c r="J20" s="158"/>
       <c r="K20" s="158"/>
-      <c r="L20" s="480"/>
+      <c r="L20" s="491"/>
       <c r="M20" s="43" t="s">
         <v>237</v>
       </c>
       <c r="N20" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="O20" s="480"/>
+      <c r="O20" s="491"/>
     </row>
     <row r="21" spans="2:15" ht="45">
-      <c r="B21" s="476" t="s">
+      <c r="B21" s="487" t="s">
         <v>239</v>
       </c>
-      <c r="C21" s="477"/>
-      <c r="D21" s="478"/>
+      <c r="C21" s="488"/>
+      <c r="D21" s="489"/>
       <c r="E21" s="184"/>
       <c r="F21" s="158"/>
       <c r="G21" s="158"/>
@@ -17068,14 +17045,14 @@
       <c r="I21" s="158"/>
       <c r="J21" s="158"/>
       <c r="K21" s="158"/>
-      <c r="L21" s="480"/>
+      <c r="L21" s="491"/>
       <c r="M21" s="43" t="s">
         <v>240</v>
       </c>
       <c r="N21" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="O21" s="480"/>
+      <c r="O21" s="491"/>
     </row>
     <row r="22" spans="2:15" ht="23.25">
       <c r="B22" s="160" t="s">
@@ -17094,12 +17071,12 @@
       <c r="I22" s="158"/>
       <c r="J22" s="158"/>
       <c r="K22" s="158"/>
-      <c r="L22" s="480"/>
-      <c r="M22" s="481" t="s">
+      <c r="L22" s="491"/>
+      <c r="M22" s="492" t="s">
         <v>218</v>
       </c>
-      <c r="N22" s="483"/>
-      <c r="O22" s="480"/>
+      <c r="N22" s="494"/>
+      <c r="O22" s="491"/>
     </row>
     <row r="23" spans="2:15" ht="23.25">
       <c r="B23" s="164" t="s">
@@ -17118,14 +17095,14 @@
       <c r="I23" s="158"/>
       <c r="J23" s="158"/>
       <c r="K23" s="158"/>
-      <c r="L23" s="480"/>
+      <c r="L23" s="491"/>
       <c r="M23" s="43" t="s">
         <v>248</v>
       </c>
       <c r="N23" s="45" t="s">
         <v>249</v>
       </c>
-      <c r="O23" s="480"/>
+      <c r="O23" s="491"/>
     </row>
     <row r="24" spans="2:15" ht="23.25">
       <c r="B24" s="164" t="s">
@@ -17144,14 +17121,14 @@
       <c r="I24" s="158"/>
       <c r="J24" s="158"/>
       <c r="K24" s="158"/>
-      <c r="L24" s="480"/>
+      <c r="L24" s="491"/>
       <c r="M24" s="43" t="s">
         <v>253</v>
       </c>
       <c r="N24" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="O24" s="480"/>
+      <c r="O24" s="491"/>
     </row>
     <row r="25" spans="2:15" ht="23.25">
       <c r="B25" s="164" t="s">
@@ -17170,12 +17147,12 @@
       <c r="I25" s="158"/>
       <c r="J25" s="158"/>
       <c r="K25" s="158"/>
-      <c r="L25" s="480"/>
-      <c r="M25" s="481" t="s">
+      <c r="L25" s="491"/>
+      <c r="M25" s="492" t="s">
         <v>227</v>
       </c>
-      <c r="N25" s="483"/>
-      <c r="O25" s="480"/>
+      <c r="N25" s="494"/>
+      <c r="O25" s="491"/>
     </row>
     <row r="26" spans="2:15" ht="23.25">
       <c r="B26" s="172" t="s">
@@ -17194,14 +17171,14 @@
       <c r="I26" s="158"/>
       <c r="J26" s="158"/>
       <c r="K26" s="158"/>
-      <c r="L26" s="480"/>
+      <c r="L26" s="491"/>
       <c r="M26" s="43" t="s">
         <v>261</v>
       </c>
       <c r="N26" s="45" t="s">
         <v>262</v>
       </c>
-      <c r="O26" s="480"/>
+      <c r="O26" s="491"/>
     </row>
     <row r="27" spans="2:15" ht="23.25">
       <c r="B27" s="164" t="s">
@@ -17220,14 +17197,14 @@
       <c r="I27" s="158"/>
       <c r="J27" s="158"/>
       <c r="K27" s="158"/>
-      <c r="L27" s="480"/>
+      <c r="L27" s="491"/>
       <c r="M27" s="43" t="s">
         <v>266</v>
       </c>
       <c r="N27" s="45" t="s">
         <v>267</v>
       </c>
-      <c r="O27" s="480"/>
+      <c r="O27" s="491"/>
     </row>
     <row r="28" spans="2:15" ht="23.25">
       <c r="B28" s="194"/>
@@ -17253,19 +17230,19 @@
       <c r="J29" s="158"/>
       <c r="K29" s="158"/>
       <c r="L29" s="158"/>
-      <c r="M29" s="473" t="s">
+      <c r="M29" s="484" t="s">
         <v>268</v>
       </c>
-      <c r="N29" s="474"/>
+      <c r="N29" s="485"/>
       <c r="O29" s="158"/>
     </row>
     <row r="30" spans="2:15" ht="45">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="498" t="s">
         <v>269</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
+      <c r="C30" s="498"/>
+      <c r="D30" s="498"/>
+      <c r="E30" s="498"/>
       <c r="F30" s="158"/>
       <c r="G30" s="158"/>
       <c r="H30" s="158"/>
@@ -17301,10 +17278,10 @@
       <c r="J31" s="158"/>
       <c r="K31" s="158"/>
       <c r="L31" s="158"/>
-      <c r="M31" s="466" t="s">
+      <c r="M31" s="482" t="s">
         <v>203</v>
       </c>
-      <c r="N31" s="467"/>
+      <c r="N31" s="483"/>
       <c r="O31" s="158"/>
     </row>
     <row r="32" spans="2:15" ht="69">
@@ -17387,10 +17364,10 @@
       <c r="J34" s="158"/>
       <c r="K34" s="158"/>
       <c r="L34" s="158"/>
-      <c r="M34" s="466" t="s">
+      <c r="M34" s="482" t="s">
         <v>218</v>
       </c>
-      <c r="N34" s="467"/>
+      <c r="N34" s="483"/>
       <c r="O34" s="158"/>
     </row>
     <row r="35" spans="1:15" ht="69">
@@ -17470,10 +17447,10 @@
       <c r="J37" s="158"/>
       <c r="K37" s="158"/>
       <c r="L37" s="158"/>
-      <c r="M37" s="466" t="s">
+      <c r="M37" s="482" t="s">
         <v>227</v>
       </c>
-      <c r="N37" s="467"/>
+      <c r="N37" s="483"/>
       <c r="O37" s="158"/>
     </row>
     <row r="38" spans="1:15" ht="69">
@@ -17548,10 +17525,10 @@
       <c r="J41" s="158"/>
       <c r="K41" s="158"/>
       <c r="L41" s="158"/>
-      <c r="M41" s="468" t="s">
+      <c r="M41" s="501" t="s">
         <v>203</v>
       </c>
-      <c r="N41" s="469"/>
+      <c r="N41" s="502"/>
       <c r="O41" s="158"/>
     </row>
     <row r="42" spans="1:15" ht="69">
@@ -17606,10 +17583,10 @@
       <c r="J44" s="158"/>
       <c r="K44" s="158"/>
       <c r="L44" s="158"/>
-      <c r="M44" s="466" t="s">
+      <c r="M44" s="482" t="s">
         <v>218</v>
       </c>
-      <c r="N44" s="467"/>
+      <c r="N44" s="483"/>
       <c r="O44" s="158"/>
     </row>
     <row r="45" spans="1:15" ht="69">
@@ -17664,10 +17641,10 @@
       <c r="J47" s="158"/>
       <c r="K47" s="158"/>
       <c r="L47" s="158"/>
-      <c r="M47" s="466" t="s">
+      <c r="M47" s="482" t="s">
         <v>227</v>
       </c>
-      <c r="N47" s="467"/>
+      <c r="N47" s="483"/>
       <c r="O47" s="158"/>
     </row>
     <row r="48" spans="1:15" ht="69">
@@ -17729,6 +17706,12 @@
   </sheetData>
   <autoFilter ref="B12:H12" xr:uid="{BD9BCBE6-71DF-4D10-AF99-FFAC47C2138B}"/>
   <mergeCells count="22">
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A2:O3"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="F13:F15"/>
     <mergeCell ref="M47:N47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="M31:N31"/>
@@ -17745,12 +17728,6 @@
     <mergeCell ref="M25:N25"/>
     <mergeCell ref="M19:N19"/>
     <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="A2:O3"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="F13:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -17779,10 +17756,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" ht="33.75">
-      <c r="D3" s="487" t="s">
+      <c r="D3" s="506" t="s">
         <v>302</v>
       </c>
-      <c r="E3" s="487"/>
+      <c r="E3" s="506"/>
     </row>
     <row r="6" spans="2:12" ht="15.75">
       <c r="B6" s="16" t="s">
@@ -18545,21 +18522,21 @@
     <row r="2" spans="1:17"/>
     <row r="3" spans="1:17"/>
     <row r="4" spans="1:17" ht="46.5">
-      <c r="A4" s="501" t="s">
+      <c r="A4" s="507" t="s">
         <v>374</v>
       </c>
-      <c r="B4" s="501"/>
-      <c r="C4" s="501"/>
-      <c r="D4" s="501"/>
-      <c r="E4" s="501"/>
-      <c r="F4" s="501"/>
-      <c r="G4" s="501"/>
-      <c r="H4" s="501"/>
-      <c r="I4" s="501"/>
-      <c r="J4" s="501"/>
-      <c r="K4" s="501"/>
-      <c r="L4" s="501"/>
-      <c r="M4" s="501"/>
+      <c r="B4" s="507"/>
+      <c r="C4" s="507"/>
+      <c r="D4" s="507"/>
+      <c r="E4" s="507"/>
+      <c r="F4" s="507"/>
+      <c r="G4" s="507"/>
+      <c r="H4" s="507"/>
+      <c r="I4" s="507"/>
+      <c r="J4" s="507"/>
+      <c r="K4" s="507"/>
+      <c r="L4" s="507"/>
+      <c r="M4" s="507"/>
       <c r="N4" s="287"/>
       <c r="O4" s="287"/>
       <c r="P4" s="287"/>
@@ -18595,20 +18572,20 @@
       <c r="Q7"/>
     </row>
     <row r="8" spans="1:17" ht="21">
-      <c r="A8" s="493" t="s">
+      <c r="A8" s="508" t="s">
         <v>375</v>
       </c>
-      <c r="B8" s="493"/>
-      <c r="C8" s="493"/>
-      <c r="D8" s="493"/>
-      <c r="E8" s="493"/>
-      <c r="F8" s="493"/>
-      <c r="G8" s="493"/>
-      <c r="H8" s="493"/>
-      <c r="I8" s="493"/>
-      <c r="J8" s="493"/>
-      <c r="K8" s="493"/>
-      <c r="L8" s="343"/>
+      <c r="B8" s="508"/>
+      <c r="C8" s="508"/>
+      <c r="D8" s="508"/>
+      <c r="E8" s="508"/>
+      <c r="F8" s="508"/>
+      <c r="G8" s="508"/>
+      <c r="H8" s="508"/>
+      <c r="I8" s="508"/>
+      <c r="J8" s="508"/>
+      <c r="K8" s="508"/>
+      <c r="L8" s="360"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:17" ht="18.75" customHeight="1">
@@ -18627,25 +18604,25 @@
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:17" ht="31.5" customHeight="1">
-      <c r="A10" s="343" t="s">
+      <c r="A10" s="360" t="s">
         <v>376</v>
       </c>
-      <c r="B10" s="343"/>
+      <c r="B10" s="360"/>
       <c r="C10" s="286"/>
-      <c r="D10" s="343" t="s">
+      <c r="D10" s="360" t="s">
         <v>377</v>
       </c>
-      <c r="E10" s="343"/>
+      <c r="E10" s="360"/>
       <c r="F10" s="286"/>
-      <c r="G10" s="343" t="s">
+      <c r="G10" s="360" t="s">
         <v>378</v>
       </c>
-      <c r="H10" s="343"/>
+      <c r="H10" s="360"/>
       <c r="I10" s="286"/>
-      <c r="J10" s="343" t="s">
+      <c r="J10" s="360" t="s">
         <v>379</v>
       </c>
-      <c r="K10" s="343"/>
+      <c r="K10" s="360"/>
       <c r="L10" s="288"/>
       <c r="M10" s="288"/>
       <c r="N10" s="286"/>
@@ -18994,13 +18971,13 @@
       <c r="H31" s="7"/>
     </row>
     <row r="32" spans="1:13" ht="21">
-      <c r="A32" s="493" t="s">
+      <c r="A32" s="508" t="s">
         <v>426</v>
       </c>
-      <c r="B32" s="493"/>
-      <c r="C32" s="493"/>
-      <c r="D32" s="493"/>
-      <c r="E32" s="493"/>
+      <c r="B32" s="508"/>
+      <c r="C32" s="508"/>
+      <c r="D32" s="508"/>
+      <c r="E32" s="508"/>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1">
       <c r="A33" s="198"/>
@@ -19033,14 +19010,14 @@
       <c r="B35" s="6">
         <v>324</v>
       </c>
-      <c r="C35" s="587">
+      <c r="C35" s="585">
         <v>102000</v>
       </c>
       <c r="D35" s="243">
         <f>Table14[[#This Row],[Unit cost]]*Table14[[#This Row],[number]]</f>
         <v>33048000</v>
       </c>
-      <c r="E35" s="502">
+      <c r="E35" s="509">
         <v>2500</v>
       </c>
     </row>
@@ -19058,7 +19035,7 @@
         <f>Table14[[#This Row],[Unit cost]]*Table14[[#This Row],[number]]</f>
         <v>18800000</v>
       </c>
-      <c r="E36" s="503"/>
+      <c r="E36" s="510"/>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1">
       <c r="A37" s="241" t="s">
@@ -19074,7 +19051,7 @@
         <f>Table14[[#This Row],[Unit cost]]*Table14[[#This Row],[number]]</f>
         <v>16000000</v>
       </c>
-      <c r="E37" s="503"/>
+      <c r="E37" s="510"/>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1">
       <c r="A38" s="242" t="s">
@@ -19090,7 +19067,7 @@
         <f>Table14[[#This Row],[Unit cost]]*Table14[[#This Row],[number]]</f>
         <v>14000000</v>
       </c>
-      <c r="E38" s="503"/>
+      <c r="E38" s="510"/>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1">
       <c r="A39" s="242" t="s">
@@ -19101,7 +19078,7 @@
       <c r="D39" s="100">
         <v>7000000</v>
       </c>
-      <c r="E39" s="503"/>
+      <c r="E39" s="510"/>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1">
       <c r="A40" s="241" t="s">
@@ -19113,7 +19090,7 @@
         <f>SUM(D35:D39)</f>
         <v>88848000</v>
       </c>
-      <c r="E40" s="504"/>
+      <c r="E40" s="511"/>
     </row>
     <row r="41" spans="1:9" ht="23.25" customHeight="1"/>
     <row r="43" spans="1:9" ht="15" customHeight="1">
@@ -19143,21 +19120,21 @@
       <c r="B44" s="6">
         <v>390</v>
       </c>
-      <c r="C44" s="587">
+      <c r="C44" s="585">
         <v>102000</v>
       </c>
       <c r="D44" s="100">
         <f>Table17[[#This Row],[Unit cost]]*Table17[[#This Row],[number]]</f>
         <v>39780000</v>
       </c>
-      <c r="E44" s="502">
+      <c r="E44" s="509">
         <v>3000</v>
       </c>
-      <c r="G44" s="493" t="s">
+      <c r="G44" s="508" t="s">
         <v>438</v>
       </c>
-      <c r="H44" s="493"/>
-      <c r="I44" s="493"/>
+      <c r="H44" s="508"/>
+      <c r="I44" s="508"/>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1">
       <c r="A45" s="241" t="s">
@@ -19173,7 +19150,7 @@
         <f>Table17[[#This Row],[Unit cost]]*Table17[[#This Row],[number]]</f>
         <v>22000000</v>
       </c>
-      <c r="E45" s="503"/>
+      <c r="E45" s="510"/>
       <c r="G45" s="7"/>
       <c r="H45" s="27"/>
       <c r="I45" s="27"/>
@@ -19192,7 +19169,7 @@
         <f>Table17[[#This Row],[Unit cost]]*Table17[[#This Row],[number]]</f>
         <v>24000000</v>
       </c>
-      <c r="E46" s="503"/>
+      <c r="E46" s="510"/>
       <c r="G46" t="s">
         <v>439</v>
       </c>
@@ -19217,7 +19194,7 @@
         <f>Table17[[#This Row],[Unit cost]]*Table17[[#This Row],[number]]</f>
         <v>18000000</v>
       </c>
-      <c r="E47" s="503"/>
+      <c r="E47" s="510"/>
       <c r="G47">
         <v>88848000</v>
       </c>
@@ -19237,7 +19214,7 @@
       <c r="D48" s="100">
         <v>8000000</v>
       </c>
-      <c r="E48" s="503"/>
+      <c r="E48" s="510"/>
       <c r="G48" s="100">
         <v>111780000</v>
       </c>
@@ -19258,7 +19235,7 @@
         <f>SUM(D44:D48)</f>
         <v>111780000</v>
       </c>
-      <c r="E49" s="504"/>
+      <c r="E49" s="511"/>
       <c r="G49">
         <v>141020000</v>
       </c>
@@ -19304,14 +19281,14 @@
       <c r="B54" s="6">
         <v>510</v>
       </c>
-      <c r="C54" s="587">
+      <c r="C54" s="585">
         <v>102000</v>
       </c>
       <c r="D54" s="100">
         <f>Table18[[#This Row],[Unit cost]]*Table18[[#This Row],[number]]</f>
         <v>52020000</v>
       </c>
-      <c r="E54" s="502">
+      <c r="E54" s="509">
         <v>3800</v>
       </c>
     </row>
@@ -19329,7 +19306,7 @@
         <f>Table18[[#This Row],[Unit cost]]*Table18[[#This Row],[number]]</f>
         <v>32000000</v>
       </c>
-      <c r="E55" s="503"/>
+      <c r="E55" s="510"/>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1">
       <c r="A56" s="241" t="s">
@@ -19345,7 +19322,7 @@
         <f>Table18[[#This Row],[Unit cost]]*Table18[[#This Row],[number]]</f>
         <v>28000000</v>
       </c>
-      <c r="E56" s="503"/>
+      <c r="E56" s="510"/>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1">
       <c r="A57" s="242" t="s">
@@ -19361,7 +19338,7 @@
         <f>Table18[[#This Row],[Unit cost]]*Table18[[#This Row],[number]]</f>
         <v>20000000</v>
       </c>
-      <c r="E57" s="503"/>
+      <c r="E57" s="510"/>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1">
       <c r="A58" s="242" t="s">
@@ -19372,7 +19349,7 @@
       <c r="D58" s="100">
         <v>9000000</v>
       </c>
-      <c r="E58" s="503"/>
+      <c r="E58" s="510"/>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1">
       <c r="A59" s="6" t="s">
@@ -19384,7 +19361,7 @@
         <f>SUM(D54:D58)</f>
         <v>141020000</v>
       </c>
-      <c r="E59" s="504"/>
+      <c r="E59" s="511"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1">
       <c r="A62" s="238" t="s">
@@ -19410,14 +19387,14 @@
       <c r="B63" s="6">
         <v>870</v>
       </c>
-      <c r="C63" s="587">
+      <c r="C63" s="585">
         <v>102000</v>
       </c>
       <c r="D63" s="100">
         <f>Table1822[[#This Row],[Unit cost]]*Table1822[[#This Row],[number]]</f>
         <v>88740000</v>
       </c>
-      <c r="E63" s="502">
+      <c r="E63" s="509">
         <v>4500</v>
       </c>
     </row>
@@ -19435,7 +19412,7 @@
         <f>Table1822[[#This Row],[Unit cost]]*Table1822[[#This Row],[number]]</f>
         <v>50000000</v>
       </c>
-      <c r="E64" s="503"/>
+      <c r="E64" s="510"/>
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="241" t="s">
@@ -19451,7 +19428,7 @@
         <f>Table1822[[#This Row],[Unit cost]]*Table1822[[#This Row],[number]]</f>
         <v>40000000</v>
       </c>
-      <c r="E65" s="503"/>
+      <c r="E65" s="510"/>
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1">
       <c r="A66" s="242" t="s">
@@ -19467,7 +19444,7 @@
         <f>Table1822[[#This Row],[Unit cost]]*Table1822[[#This Row],[number]]</f>
         <v>28000000</v>
       </c>
-      <c r="E66" s="503"/>
+      <c r="E66" s="510"/>
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="242" t="s">
@@ -19478,7 +19455,7 @@
       <c r="D67" s="100">
         <v>10000000</v>
       </c>
-      <c r="E67" s="503"/>
+      <c r="E67" s="510"/>
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="6" t="s">
@@ -19490,7 +19467,7 @@
         <f>SUM(D63:D67)</f>
         <v>216740000</v>
       </c>
-      <c r="E68" s="504"/>
+      <c r="E68" s="511"/>
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="7"/>
@@ -19537,26 +19514,26 @@
       <c r="C73" s="27"/>
     </row>
     <row r="74" spans="1:21" ht="21.75" customHeight="1">
-      <c r="A74" s="494" t="s">
+      <c r="A74" s="520" t="s">
         <v>441</v>
       </c>
-      <c r="B74" s="494"/>
-      <c r="C74" s="494"/>
-      <c r="D74" s="494"/>
-      <c r="E74" s="494"/>
-      <c r="F74" s="494"/>
-      <c r="G74" s="494"/>
-      <c r="H74" s="494"/>
-      <c r="I74" s="494"/>
+      <c r="B74" s="520"/>
+      <c r="C74" s="520"/>
+      <c r="D74" s="520"/>
+      <c r="E74" s="520"/>
+      <c r="F74" s="520"/>
+      <c r="G74" s="520"/>
+      <c r="H74" s="520"/>
+      <c r="I74" s="520"/>
       <c r="J74" s="153"/>
-      <c r="L74" s="493" t="s">
+      <c r="L74" s="508" t="s">
         <v>442</v>
       </c>
-      <c r="M74" s="493"/>
-      <c r="N74" s="493"/>
-      <c r="O74" s="493"/>
-      <c r="P74" s="493"/>
-      <c r="Q74" s="493"/>
+      <c r="M74" s="508"/>
+      <c r="N74" s="508"/>
+      <c r="O74" s="508"/>
+      <c r="P74" s="508"/>
+      <c r="Q74" s="508"/>
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="282"/>
@@ -19622,14 +19599,14 @@
       <c r="B77" s="6">
         <v>324</v>
       </c>
-      <c r="C77" s="505">
+      <c r="C77" s="512">
         <v>260</v>
       </c>
       <c r="D77" s="6">
         <f>B77*C77</f>
         <v>84240</v>
       </c>
-      <c r="E77" s="505">
+      <c r="E77" s="512">
         <v>8.3000000000000007</v>
       </c>
       <c r="F77" s="257">
@@ -19643,13 +19620,13 @@
         <f>F77-G77</f>
         <v>28942.000000000116</v>
       </c>
-      <c r="I77" s="505">
+      <c r="I77" s="512">
         <v>25550</v>
       </c>
       <c r="L77" s="99" t="s">
         <v>457</v>
       </c>
-      <c r="M77" s="505">
+      <c r="M77" s="512">
         <v>365</v>
       </c>
       <c r="N77" s="242">
@@ -19674,12 +19651,12 @@
       <c r="B78" s="6">
         <v>390</v>
       </c>
-      <c r="C78" s="506"/>
+      <c r="C78" s="513"/>
       <c r="D78" s="6">
         <f>B78*C77</f>
         <v>101400</v>
       </c>
-      <c r="E78" s="506"/>
+      <c r="E78" s="513"/>
       <c r="F78" s="6">
         <f>E77*D78</f>
         <v>841620.00000000012</v>
@@ -19691,11 +19668,11 @@
         <f t="shared" ref="H78:H80" si="0">F78-G78</f>
         <v>3808.0000000001164</v>
       </c>
-      <c r="I78" s="506"/>
+      <c r="I78" s="513"/>
       <c r="L78" s="257" t="s">
         <v>458</v>
       </c>
-      <c r="M78" s="506"/>
+      <c r="M78" s="513"/>
       <c r="N78" s="242">
         <v>841.62</v>
       </c>
@@ -19718,12 +19695,12 @@
       <c r="B79" s="6">
         <v>510</v>
       </c>
-      <c r="C79" s="506"/>
+      <c r="C79" s="513"/>
       <c r="D79" s="6">
         <f>C77*B79</f>
         <v>132600</v>
       </c>
-      <c r="E79" s="506"/>
+      <c r="E79" s="513"/>
       <c r="F79" s="6">
         <f>E77*D79</f>
         <v>1100580</v>
@@ -19735,11 +19712,11 @@
         <f t="shared" si="0"/>
         <v>53315</v>
       </c>
-      <c r="I79" s="506"/>
+      <c r="I79" s="513"/>
       <c r="L79" s="257" t="s">
         <v>459</v>
       </c>
-      <c r="M79" s="506"/>
+      <c r="M79" s="513"/>
       <c r="N79" s="242">
         <v>1100.58</v>
       </c>
@@ -19762,12 +19739,12 @@
       <c r="B80" s="6">
         <v>870</v>
       </c>
-      <c r="C80" s="507"/>
+      <c r="C80" s="514"/>
       <c r="D80" s="6">
         <f>C77*B80</f>
         <v>226200</v>
       </c>
-      <c r="E80" s="507"/>
+      <c r="E80" s="514"/>
       <c r="F80" s="6">
         <f>E77*D80</f>
         <v>1877460.0000000002</v>
@@ -19779,11 +19756,11 @@
         <f t="shared" si="0"/>
         <v>306563.00000000023</v>
       </c>
-      <c r="I80" s="507"/>
+      <c r="I80" s="514"/>
       <c r="L80" s="257" t="s">
         <v>460</v>
       </c>
-      <c r="M80" s="507"/>
+      <c r="M80" s="514"/>
       <c r="N80" s="260">
         <v>1877.46</v>
       </c>
@@ -19802,15 +19779,15 @@
     <row r="81" spans="1:17" ht="21" customHeight="1"/>
     <row r="83" spans="1:17" ht="27.75" customHeight="1"/>
     <row r="84" spans="1:17" ht="22.5" customHeight="1">
-      <c r="A84" s="493" t="s">
+      <c r="A84" s="508" t="s">
         <v>461</v>
       </c>
-      <c r="B84" s="493"/>
-      <c r="C84" s="493"/>
-      <c r="D84" s="493"/>
-      <c r="E84" s="493"/>
-      <c r="F84" s="493"/>
-      <c r="G84" s="493"/>
+      <c r="B84" s="508"/>
+      <c r="C84" s="508"/>
+      <c r="D84" s="508"/>
+      <c r="E84" s="508"/>
+      <c r="F84" s="508"/>
+      <c r="G84" s="508"/>
     </row>
     <row r="86" spans="1:17" ht="15" customHeight="1">
       <c r="A86" s="99" t="s">
@@ -19852,7 +19829,7 @@
         <f>C87-D87</f>
         <v>28.942000000000007</v>
       </c>
-      <c r="F87" s="505">
+      <c r="F87" s="512">
         <v>70</v>
       </c>
       <c r="G87" s="259">
@@ -19877,7 +19854,7 @@
         <f t="shared" ref="E88:E90" si="1">C88-D88</f>
         <v>3.8079999999999927</v>
       </c>
-      <c r="F88" s="506"/>
+      <c r="F88" s="513"/>
       <c r="G88" s="259">
         <f>E88+F87</f>
         <v>73.807999999999993</v>
@@ -19900,7 +19877,7 @@
         <f t="shared" si="1"/>
         <v>53.314999999999827</v>
       </c>
-      <c r="F89" s="506"/>
+      <c r="F89" s="513"/>
       <c r="G89" s="259">
         <f>E89+F87</f>
         <v>123.31499999999983</v>
@@ -19923,7 +19900,7 @@
         <f t="shared" si="1"/>
         <v>306.5630000000001</v>
       </c>
-      <c r="F90" s="507"/>
+      <c r="F90" s="514"/>
       <c r="G90" s="259">
         <f>E90+F87</f>
         <v>376.5630000000001</v>
@@ -19955,14 +19932,14 @@
       <c r="Q92"/>
     </row>
     <row r="95" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A95" s="493" t="s">
+      <c r="A95" s="508" t="s">
         <v>468</v>
       </c>
-      <c r="B95" s="493"/>
-      <c r="C95" s="493"/>
-      <c r="D95" s="493"/>
-      <c r="E95" s="493"/>
-      <c r="F95" s="493"/>
+      <c r="B95" s="508"/>
+      <c r="C95" s="508"/>
+      <c r="D95" s="508"/>
+      <c r="E95" s="508"/>
+      <c r="F95" s="508"/>
       <c r="G95" s="286"/>
       <c r="H95" s="286"/>
       <c r="I95" s="286"/>
@@ -20002,14 +19979,14 @@
       <c r="B98" s="259">
         <v>98.942000000000007</v>
       </c>
-      <c r="C98" s="498">
+      <c r="C98" s="524">
         <v>30</v>
       </c>
       <c r="D98" s="264">
         <f>B98*C98</f>
         <v>2968.26</v>
       </c>
-      <c r="E98" s="495">
+      <c r="E98" s="521">
         <v>365</v>
       </c>
       <c r="F98" s="296">
@@ -20024,12 +20001,12 @@
       <c r="B99" s="264">
         <v>73.807999999999993</v>
       </c>
-      <c r="C99" s="499"/>
+      <c r="C99" s="525"/>
       <c r="D99" s="259">
         <f>B99*C98</f>
         <v>2214.2399999999998</v>
       </c>
-      <c r="E99" s="496"/>
+      <c r="E99" s="522"/>
       <c r="F99" s="259">
         <f>D99*E98</f>
         <v>808197.6</v>
@@ -20042,12 +20019,12 @@
       <c r="B100" s="259">
         <v>123.31499999999983</v>
       </c>
-      <c r="C100" s="499"/>
+      <c r="C100" s="525"/>
       <c r="D100" s="259">
         <f>B100*C98</f>
         <v>3699.4499999999948</v>
       </c>
-      <c r="E100" s="496"/>
+      <c r="E100" s="522"/>
       <c r="F100" s="259">
         <f>D100*E98</f>
         <v>1350299.2499999981</v>
@@ -20060,12 +20037,12 @@
       <c r="B101" s="259">
         <v>376.5630000000001</v>
       </c>
-      <c r="C101" s="500"/>
+      <c r="C101" s="526"/>
       <c r="D101" s="259">
         <f>B101*C98</f>
         <v>11296.890000000003</v>
       </c>
-      <c r="E101" s="497"/>
+      <c r="E101" s="523"/>
       <c r="F101" s="259">
         <f>D101*E98</f>
         <v>4123364.850000001</v>
@@ -20084,15 +20061,15 @@
       <c r="C105" s="7"/>
     </row>
     <row r="106" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A106" s="493" t="s">
+      <c r="A106" s="508" t="s">
         <v>474</v>
       </c>
-      <c r="B106" s="493"/>
-      <c r="C106" s="493"/>
-      <c r="D106" s="493"/>
-      <c r="E106" s="493"/>
-      <c r="F106" s="493"/>
-      <c r="G106" s="493"/>
+      <c r="B106" s="508"/>
+      <c r="C106" s="508"/>
+      <c r="D106" s="508"/>
+      <c r="E106" s="508"/>
+      <c r="F106" s="508"/>
+      <c r="G106" s="508"/>
     </row>
     <row r="110" spans="1:7" ht="15" customHeight="1">
       <c r="B110" s="285" t="s">
@@ -20159,20 +20136,20 @@
       </c>
     </row>
     <row r="142" spans="2:6" ht="15" customHeight="1">
-      <c r="B142" s="488" t="s">
+      <c r="B142" s="515" t="s">
         <v>482</v>
       </c>
-      <c r="C142" s="488"/>
-      <c r="D142" s="488"/>
-      <c r="E142" s="488"/>
-      <c r="F142" s="488"/>
+      <c r="C142" s="515"/>
+      <c r="D142" s="515"/>
+      <c r="E142" s="515"/>
+      <c r="F142" s="515"/>
     </row>
     <row r="143" spans="2:6" ht="15" customHeight="1">
-      <c r="B143" s="488"/>
-      <c r="C143" s="488"/>
-      <c r="D143" s="488"/>
-      <c r="E143" s="488"/>
-      <c r="F143" s="488"/>
+      <c r="B143" s="515"/>
+      <c r="C143" s="515"/>
+      <c r="D143" s="515"/>
+      <c r="E143" s="515"/>
+      <c r="F143" s="515"/>
     </row>
     <row r="146" spans="2:6" ht="15" customHeight="1">
       <c r="B146" s="313" t="s">
@@ -20348,15 +20325,15 @@
       <c r="F158" s="323"/>
     </row>
     <row r="159" spans="2:6" ht="15" customHeight="1">
-      <c r="B159" s="489" t="s">
+      <c r="B159" s="516" t="s">
         <v>523</v>
       </c>
-      <c r="C159" s="490"/>
-      <c r="D159" s="490"/>
-      <c r="E159" s="491" t="s">
+      <c r="C159" s="517"/>
+      <c r="D159" s="517"/>
+      <c r="E159" s="518" t="s">
         <v>524</v>
       </c>
-      <c r="F159" s="492"/>
+      <c r="F159" s="519"/>
     </row>
     <row r="160" spans="2:6" ht="15" customHeight="1">
       <c r="B160" s="314" t="s">
@@ -20415,6 +20392,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B142:F143"/>
+    <mergeCell ref="B159:D159"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="A106:G106"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="C98:C101"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A95:F95"/>
     <mergeCell ref="E54:E59"/>
@@ -20431,13 +20415,6 @@
     <mergeCell ref="E77:E80"/>
     <mergeCell ref="C77:C80"/>
     <mergeCell ref="I77:I80"/>
-    <mergeCell ref="B142:F143"/>
-    <mergeCell ref="B159:D159"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="A106:G106"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="C98:C101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -20470,14 +20447,14 @@
       <c r="A1" s="153"/>
     </row>
     <row r="2" spans="1:7" ht="26.25">
-      <c r="B2" s="508" t="s">
+      <c r="B2" s="527" t="s">
         <v>533</v>
       </c>
-      <c r="C2" s="508"/>
-      <c r="D2" s="508"/>
-      <c r="E2" s="508"/>
-      <c r="F2" s="508"/>
-      <c r="G2" s="508"/>
+      <c r="C2" s="527"/>
+      <c r="D2" s="527"/>
+      <c r="E2" s="527"/>
+      <c r="F2" s="527"/>
+      <c r="G2" s="527"/>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="5"/>
@@ -20582,11 +20559,11 @@
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="B10" s="509" t="s">
+      <c r="B10" s="528" t="s">
         <v>543</v>
       </c>
-      <c r="C10" s="510"/>
-      <c r="D10" s="510"/>
+      <c r="C10" s="529"/>
+      <c r="D10" s="529"/>
       <c r="E10" s="106"/>
       <c r="F10" s="7"/>
     </row>
@@ -20661,11 +20638,11 @@
       </c>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="511" t="s">
+      <c r="B19" s="530" t="s">
         <v>548</v>
       </c>
-      <c r="C19" s="512"/>
-      <c r="D19" s="512"/>
+      <c r="C19" s="531"/>
+      <c r="D19" s="531"/>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="102" t="s">
@@ -20750,24 +20727,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="36.75" customHeight="1">
-      <c r="C2" s="551" t="s">
+      <c r="C2" s="533" t="s">
         <v>553</v>
       </c>
-      <c r="D2" s="551"/>
-      <c r="E2" s="551"/>
+      <c r="D2" s="533"/>
+      <c r="E2" s="533"/>
     </row>
     <row r="3" spans="1:5" ht="36.75" customHeight="1">
-      <c r="C3" s="564" t="s">
+      <c r="C3" s="546" t="s">
         <v>554</v>
       </c>
-      <c r="D3" s="564"/>
+      <c r="D3" s="546"/>
       <c r="E3" s="305"/>
     </row>
     <row r="4" spans="1:5" ht="36.75" customHeight="1">
-      <c r="C4" s="564" t="s">
+      <c r="C4" s="546" t="s">
         <v>555</v>
       </c>
-      <c r="D4" s="564"/>
+      <c r="D4" s="546"/>
       <c r="E4" s="305"/>
     </row>
     <row r="7" spans="1:5" s="9" customFormat="1" ht="50.25" customHeight="1">
@@ -20850,10 +20827,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="C17" s="565" t="s">
+      <c r="C17" s="547" t="s">
         <v>575</v>
       </c>
-      <c r="D17" s="494"/>
+      <c r="D17" s="520"/>
     </row>
     <row r="18" spans="1:9" ht="11.25" customHeight="1"/>
     <row r="19" spans="1:9" ht="28.5" customHeight="1">
@@ -20863,40 +20840,40 @@
       <c r="D19" s="116" t="s">
         <v>577</v>
       </c>
-      <c r="E19" s="556" t="s">
+      <c r="E19" s="538" t="s">
         <v>578</v>
       </c>
-      <c r="F19" s="557"/>
+      <c r="F19" s="539"/>
       <c r="G19" s="117" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1">
-      <c r="A20" s="554" t="s">
+      <c r="A20" s="536" t="s">
         <v>580</v>
       </c>
-      <c r="B20" s="555"/>
+      <c r="B20" s="537"/>
       <c r="C20" s="118">
         <v>130</v>
       </c>
       <c r="D20" s="119">
         <v>250</v>
       </c>
-      <c r="E20" s="558">
+      <c r="E20" s="540">
         <f>D20-C20</f>
         <v>120</v>
       </c>
-      <c r="F20" s="559"/>
+      <c r="F20" s="541"/>
       <c r="G20" s="145">
         <f>D20/(C20+D20)</f>
         <v>0.65789473684210531</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="554" t="s">
+      <c r="A21" s="536" t="s">
         <v>581</v>
       </c>
-      <c r="B21" s="555"/>
+      <c r="B21" s="537"/>
       <c r="C21" s="268">
         <f>130*50000/1000000</f>
         <v>6.5</v>
@@ -20905,21 +20882,21 @@
         <f>250*50000/1000000</f>
         <v>12.5</v>
       </c>
-      <c r="E21" s="560">
+      <c r="E21" s="542">
         <f t="shared" ref="E21:E22" si="0">D21-C21</f>
         <v>6</v>
       </c>
-      <c r="F21" s="561"/>
+      <c r="F21" s="543"/>
       <c r="G21" s="146">
         <f>D21/(C21+D21)</f>
         <v>0.65789473684210531</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="36" customHeight="1">
-      <c r="A22" s="552" t="s">
+      <c r="A22" s="534" t="s">
         <v>582</v>
       </c>
-      <c r="B22" s="553"/>
+      <c r="B22" s="535"/>
       <c r="C22" s="268">
         <f>130*15000/1000000</f>
         <v>1.95</v>
@@ -20927,11 +20904,11 @@
       <c r="D22" s="119">
         <v>0</v>
       </c>
-      <c r="E22" s="562">
+      <c r="E22" s="544">
         <f>-D22+C22</f>
         <v>1.95</v>
       </c>
-      <c r="F22" s="563"/>
+      <c r="F22" s="545"/>
       <c r="G22" s="147">
         <f>1</f>
         <v>1</v>
@@ -20939,44 +20916,44 @@
     </row>
     <row r="23" spans="1:9"/>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="C26" s="550" t="s">
+      <c r="C26" s="532" t="s">
         <v>583</v>
       </c>
-      <c r="D26" s="550"/>
+      <c r="D26" s="532"/>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
-      <c r="C27" s="550"/>
-      <c r="D27" s="550"/>
+      <c r="C27" s="532"/>
+      <c r="D27" s="532"/>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
-      <c r="B29" s="513" t="s">
+      <c r="B29" s="574" t="s">
         <v>483</v>
       </c>
-      <c r="C29" s="513" t="s">
+      <c r="C29" s="574" t="s">
         <v>484</v>
       </c>
-      <c r="D29" s="515" t="s">
+      <c r="D29" s="576" t="s">
         <v>485</v>
       </c>
-      <c r="E29" s="541" t="s">
+      <c r="E29" s="551" t="s">
         <v>486</v>
       </c>
-      <c r="F29" s="541"/>
-      <c r="G29" s="542"/>
-      <c r="H29" s="541" t="s">
+      <c r="F29" s="551"/>
+      <c r="G29" s="552"/>
+      <c r="H29" s="551" t="s">
         <v>487</v>
       </c>
-      <c r="I29" s="542"/>
+      <c r="I29" s="552"/>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1">
-      <c r="B30" s="528"/>
-      <c r="C30" s="514"/>
-      <c r="D30" s="516"/>
-      <c r="E30" s="543"/>
-      <c r="F30" s="543"/>
-      <c r="G30" s="544"/>
-      <c r="H30" s="543"/>
-      <c r="I30" s="544"/>
+      <c r="B30" s="584"/>
+      <c r="C30" s="575"/>
+      <c r="D30" s="577"/>
+      <c r="E30" s="553"/>
+      <c r="F30" s="553"/>
+      <c r="G30" s="554"/>
+      <c r="H30" s="553"/>
+      <c r="I30" s="554"/>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1">
       <c r="B31" s="337" t="s">
@@ -20985,18 +20962,18 @@
       <c r="C31" s="338" t="s">
         <v>585</v>
       </c>
-      <c r="D31" s="527" t="s">
+      <c r="D31" s="583" t="s">
         <v>586</v>
       </c>
-      <c r="E31" s="526" t="s">
+      <c r="E31" s="558" t="s">
         <v>587</v>
       </c>
-      <c r="F31" s="545"/>
-      <c r="G31" s="546"/>
-      <c r="H31" s="547" t="s">
+      <c r="F31" s="559"/>
+      <c r="G31" s="560"/>
+      <c r="H31" s="555" t="s">
         <v>588</v>
       </c>
-      <c r="I31" s="548"/>
+      <c r="I31" s="556"/>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1">
       <c r="B32" s="337" t="s">
@@ -21005,14 +20982,14 @@
       <c r="C32" s="339" t="s">
         <v>590</v>
       </c>
-      <c r="D32" s="527"/>
-      <c r="E32" s="526"/>
-      <c r="F32" s="545"/>
-      <c r="G32" s="546"/>
-      <c r="H32" s="549" t="s">
+      <c r="D32" s="583"/>
+      <c r="E32" s="558"/>
+      <c r="F32" s="559"/>
+      <c r="G32" s="560"/>
+      <c r="H32" s="557" t="s">
         <v>591</v>
       </c>
-      <c r="I32" s="548"/>
+      <c r="I32" s="556"/>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1">
       <c r="B33" s="337" t="s">
@@ -21021,98 +20998,98 @@
       <c r="C33" s="339" t="s">
         <v>593</v>
       </c>
-      <c r="D33" s="527"/>
-      <c r="E33" s="529"/>
-      <c r="F33" s="539"/>
-      <c r="G33" s="344"/>
-      <c r="H33" s="549" t="s">
+      <c r="D33" s="583"/>
+      <c r="E33" s="548"/>
+      <c r="F33" s="549"/>
+      <c r="G33" s="361"/>
+      <c r="H33" s="557" t="s">
         <v>594</v>
       </c>
-      <c r="I33" s="548"/>
+      <c r="I33" s="556"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1">
-      <c r="B34" s="526" t="s">
+      <c r="B34" s="558" t="s">
         <v>595</v>
       </c>
       <c r="C34" s="339" t="s">
         <v>596</v>
       </c>
-      <c r="D34" s="524" t="s">
+      <c r="D34" s="581" t="s">
         <v>597</v>
       </c>
-      <c r="E34" s="529"/>
-      <c r="F34" s="539"/>
-      <c r="G34" s="344"/>
-      <c r="H34" s="549"/>
-      <c r="I34" s="548"/>
+      <c r="E34" s="548"/>
+      <c r="F34" s="549"/>
+      <c r="G34" s="361"/>
+      <c r="H34" s="557"/>
+      <c r="I34" s="556"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1">
-      <c r="B35" s="526"/>
+      <c r="B35" s="558"/>
       <c r="C35" s="339" t="s">
         <v>598</v>
       </c>
-      <c r="D35" s="524"/>
-      <c r="E35" s="529"/>
-      <c r="F35" s="539"/>
-      <c r="G35" s="344"/>
-      <c r="H35" s="549"/>
-      <c r="I35" s="548"/>
+      <c r="D35" s="581"/>
+      <c r="E35" s="548"/>
+      <c r="F35" s="549"/>
+      <c r="G35" s="361"/>
+      <c r="H35" s="557"/>
+      <c r="I35" s="556"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1">
       <c r="B36" s="337"/>
       <c r="C36" s="336" t="s">
         <v>512</v>
       </c>
-      <c r="D36" s="523" t="s">
+      <c r="D36" s="580" t="s">
         <v>599</v>
       </c>
-      <c r="E36" s="533" t="s">
+      <c r="E36" s="561" t="s">
         <v>513</v>
       </c>
-      <c r="F36" s="534"/>
-      <c r="G36" s="535"/>
-      <c r="H36" s="539"/>
-      <c r="I36" s="530"/>
+      <c r="F36" s="562"/>
+      <c r="G36" s="563"/>
+      <c r="H36" s="549"/>
+      <c r="I36" s="550"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1">
       <c r="B37" s="337"/>
       <c r="C37" s="338" t="s">
         <v>600</v>
       </c>
-      <c r="D37" s="524"/>
-      <c r="E37" s="526" t="s">
+      <c r="D37" s="581"/>
+      <c r="E37" s="558" t="s">
         <v>601</v>
       </c>
-      <c r="F37" s="545"/>
-      <c r="G37" s="546"/>
-      <c r="H37" s="529"/>
-      <c r="I37" s="530"/>
+      <c r="F37" s="559"/>
+      <c r="G37" s="560"/>
+      <c r="H37" s="548"/>
+      <c r="I37" s="550"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1">
       <c r="B38" s="337"/>
       <c r="C38" s="339" t="s">
         <v>602</v>
       </c>
-      <c r="D38" s="525"/>
-      <c r="E38" s="526"/>
-      <c r="F38" s="545"/>
-      <c r="G38" s="546"/>
-      <c r="H38" s="529"/>
-      <c r="I38" s="530"/>
+      <c r="D38" s="582"/>
+      <c r="E38" s="558"/>
+      <c r="F38" s="559"/>
+      <c r="G38" s="560"/>
+      <c r="H38" s="548"/>
+      <c r="I38" s="550"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1">
       <c r="B39" s="337"/>
       <c r="C39" s="339" t="s">
         <v>603</v>
       </c>
-      <c r="D39" s="525"/>
-      <c r="E39" s="526" t="s">
+      <c r="D39" s="582"/>
+      <c r="E39" s="558" t="s">
         <v>604</v>
       </c>
-      <c r="F39" s="545"/>
-      <c r="G39" s="546"/>
-      <c r="H39" s="529"/>
-      <c r="I39" s="530"/>
+      <c r="F39" s="559"/>
+      <c r="G39" s="560"/>
+      <c r="H39" s="548"/>
+      <c r="I39" s="550"/>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1">
       <c r="B40" s="337"/>
@@ -21120,83 +21097,83 @@
         <v>605</v>
       </c>
       <c r="D40" s="7"/>
-      <c r="E40" s="526"/>
-      <c r="F40" s="545"/>
-      <c r="G40" s="546"/>
-      <c r="H40" s="529"/>
-      <c r="I40" s="530"/>
+      <c r="E40" s="558"/>
+      <c r="F40" s="559"/>
+      <c r="G40" s="560"/>
+      <c r="H40" s="548"/>
+      <c r="I40" s="550"/>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1">
       <c r="B41" s="337"/>
       <c r="C41" s="306"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="529"/>
-      <c r="F41" s="539"/>
-      <c r="G41" s="530"/>
-      <c r="H41" s="529"/>
-      <c r="I41" s="530"/>
+      <c r="E41" s="548"/>
+      <c r="F41" s="549"/>
+      <c r="G41" s="550"/>
+      <c r="H41" s="548"/>
+      <c r="I41" s="550"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1">
-      <c r="B42" s="517" t="s">
+      <c r="B42" s="578" t="s">
         <v>523</v>
       </c>
-      <c r="C42" s="518"/>
-      <c r="D42" s="533" t="s">
+      <c r="C42" s="579"/>
+      <c r="D42" s="561" t="s">
         <v>524</v>
       </c>
-      <c r="E42" s="534"/>
-      <c r="F42" s="534"/>
-      <c r="G42" s="534"/>
-      <c r="H42" s="534"/>
-      <c r="I42" s="535"/>
+      <c r="E42" s="562"/>
+      <c r="F42" s="562"/>
+      <c r="G42" s="562"/>
+      <c r="H42" s="562"/>
+      <c r="I42" s="563"/>
     </row>
     <row r="43" spans="2:9" ht="15" customHeight="1">
-      <c r="B43" s="519" t="s">
+      <c r="B43" s="568" t="s">
         <v>606</v>
       </c>
-      <c r="C43" s="520"/>
-      <c r="D43" s="519" t="s">
+      <c r="C43" s="570"/>
+      <c r="D43" s="568" t="s">
         <v>607</v>
       </c>
-      <c r="E43" s="536"/>
-      <c r="F43" s="536"/>
-      <c r="G43" s="536"/>
-      <c r="H43" s="536"/>
-      <c r="I43" s="520"/>
+      <c r="E43" s="569"/>
+      <c r="F43" s="569"/>
+      <c r="G43" s="569"/>
+      <c r="H43" s="569"/>
+      <c r="I43" s="570"/>
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1">
-      <c r="B44" s="521" t="s">
+      <c r="B44" s="564" t="s">
         <v>608</v>
       </c>
-      <c r="C44" s="522"/>
-      <c r="D44" s="521" t="s">
+      <c r="C44" s="565"/>
+      <c r="D44" s="564" t="s">
         <v>609</v>
       </c>
-      <c r="E44" s="538"/>
-      <c r="F44" s="538"/>
-      <c r="G44" s="538"/>
-      <c r="H44" s="538"/>
-      <c r="I44" s="522"/>
+      <c r="E44" s="572"/>
+      <c r="F44" s="572"/>
+      <c r="G44" s="572"/>
+      <c r="H44" s="572"/>
+      <c r="I44" s="565"/>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1">
-      <c r="B45" s="521" t="s">
+      <c r="B45" s="564" t="s">
         <v>610</v>
       </c>
-      <c r="C45" s="522"/>
-      <c r="D45" s="521" t="s">
+      <c r="C45" s="565"/>
+      <c r="D45" s="564" t="s">
         <v>611</v>
       </c>
-      <c r="E45" s="537"/>
-      <c r="F45" s="537"/>
-      <c r="G45" s="537"/>
-      <c r="H45" s="537"/>
-      <c r="I45" s="522"/>
+      <c r="E45" s="571"/>
+      <c r="F45" s="571"/>
+      <c r="G45" s="571"/>
+      <c r="H45" s="571"/>
+      <c r="I45" s="565"/>
     </row>
     <row r="46" spans="2:9" ht="15" customHeight="1">
-      <c r="B46" s="521" t="s">
+      <c r="B46" s="564" t="s">
         <v>612</v>
       </c>
-      <c r="C46" s="522"/>
+      <c r="C46" s="565"/>
       <c r="D46" s="258"/>
       <c r="E46" s="258"/>
       <c r="F46" s="258"/>
@@ -21205,39 +21182,53 @@
       <c r="I46" s="258"/>
     </row>
     <row r="47" spans="2:9" ht="15" customHeight="1">
-      <c r="B47" s="529"/>
-      <c r="C47" s="530"/>
-      <c r="D47" s="529"/>
-      <c r="E47" s="539"/>
-      <c r="F47" s="539"/>
-      <c r="G47" s="539"/>
-      <c r="H47" s="539"/>
-      <c r="I47" s="530"/>
+      <c r="B47" s="548"/>
+      <c r="C47" s="550"/>
+      <c r="D47" s="548"/>
+      <c r="E47" s="549"/>
+      <c r="F47" s="549"/>
+      <c r="G47" s="549"/>
+      <c r="H47" s="549"/>
+      <c r="I47" s="550"/>
     </row>
     <row r="48" spans="2:9" ht="15" customHeight="1">
-      <c r="B48" s="531"/>
-      <c r="C48" s="532"/>
-      <c r="D48" s="531"/>
-      <c r="E48" s="540"/>
-      <c r="F48" s="540"/>
-      <c r="G48" s="540"/>
-      <c r="H48" s="540"/>
-      <c r="I48" s="532"/>
+      <c r="B48" s="566"/>
+      <c r="C48" s="567"/>
+      <c r="D48" s="566"/>
+      <c r="E48" s="573"/>
+      <c r="F48" s="573"/>
+      <c r="G48" s="573"/>
+      <c r="H48" s="573"/>
+      <c r="I48" s="567"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D45:I45"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D48:I48"/>
+    <mergeCell ref="E29:G30"/>
+    <mergeCell ref="E31:G32"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="E39:G40"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E34:F34"/>
@@ -21254,32 +21245,18 @@
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="H39:I39"/>
     <mergeCell ref="H40:I40"/>
-    <mergeCell ref="E29:G30"/>
-    <mergeCell ref="E31:G32"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="E39:G40"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D42:I42"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D45:I45"/>
-    <mergeCell ref="D44:I44"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D48:I48"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
